--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1358">
   <si>
     <t>_Id</t>
   </si>
@@ -4074,9 +4074,6 @@
     <t>10239</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>虚无水龙谷</t>
   </si>
   <si>
@@ -4086,7 +4083,10 @@
     <t>虚无战锤，35升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210090,1009,506,202008,202003,507</t>
+    <t>202002,106,504,210090,1009,506,202008,202003,507,508</t>
+  </si>
+  <si>
+    <t>10,18000,98000,600000,140000,900000,1200000,1000000,1000000,2000000</t>
   </si>
   <si>
     <t>10240</t>
@@ -4787,7 +4787,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4804,10 +4804,12 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -6481,10 +6483,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6510,10 +6512,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6539,10 +6541,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6568,10 +6570,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="12" t="s">
+      <c r="J49" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6597,10 +6599,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="12" t="s">
+      <c r="K50" s="13" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6629,10 +6631,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6658,10 +6660,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="K52" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6687,10 +6689,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6716,10 +6718,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="12" t="s">
+      <c r="K54" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6745,10 +6747,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="12" t="s">
+      <c r="K55" s="13" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6777,10 +6779,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="12" t="s">
+      <c r="K56" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6809,10 +6811,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="12" t="s">
+      <c r="J57" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="12" t="s">
+      <c r="K57" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6841,10 +6843,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="12" t="s">
+      <c r="J58" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="12" t="s">
+      <c r="K58" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6873,10 +6875,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="12" t="s">
+      <c r="J59" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="12" t="s">
+      <c r="K59" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6905,10 +6907,10 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="12" t="s">
+      <c r="J60" s="13" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="12" t="s">
+      <c r="K60" s="13" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
@@ -6938,10 +6940,10 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="J61" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="13" t="s">
+      <c r="K61" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L61" s="2" t="s">
@@ -6971,10 +6973,10 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="J62" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="13" t="s">
+      <c r="K62" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L62" s="2" t="s">
@@ -7004,10 +7006,10 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="13" t="s">
+      <c r="J63" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="13" t="s">
+      <c r="K63" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L63" s="2" t="s">
@@ -7037,10 +7039,10 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="13" t="s">
+      <c r="J64" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="13" t="s">
+      <c r="K64" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L64" s="2" t="s">
@@ -7070,10 +7072,10 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="J65" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="13" t="s">
+      <c r="K65" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L65" s="2" t="s">
@@ -7102,10 +7104,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="13" t="s">
+      <c r="J66" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="13" t="s">
+      <c r="K66" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -7134,10 +7136,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="J67" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="13" t="s">
+      <c r="K67" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -7166,10 +7168,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="J68" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="13" t="s">
+      <c r="K68" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -7198,10 +7200,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="J69" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="13" t="s">
+      <c r="K69" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -7230,10 +7232,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="13" t="s">
+      <c r="J70" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="13" t="s">
+      <c r="K70" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -7262,10 +7264,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="13" t="s">
+      <c r="K71" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -7294,10 +7296,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="13" t="s">
+      <c r="J72" s="14" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="13" t="s">
+      <c r="K72" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -7326,10 +7328,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="13" t="s">
+      <c r="J73" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="13" t="s">
+      <c r="K73" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -7358,10 +7360,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="13" t="s">
+      <c r="J74" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="13" t="s">
+      <c r="K74" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7390,10 +7392,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="13" t="s">
+      <c r="J75" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="13" t="s">
+      <c r="K75" s="14" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7422,10 +7424,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="13" t="s">
+      <c r="J76" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="13" t="s">
+      <c r="K76" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7454,10 +7456,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="13" t="s">
+      <c r="K77" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7486,10 +7488,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="13" t="s">
+      <c r="J78" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="13" t="s">
+      <c r="K78" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7518,10 +7520,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="13" t="s">
+      <c r="J79" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="13" t="s">
+      <c r="K79" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7550,10 +7552,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="13" t="s">
+      <c r="J80" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="13" t="s">
+      <c r="K80" s="14" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7582,10 +7584,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="13" t="s">
+      <c r="J81" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="13" t="s">
+      <c r="K81" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7614,10 +7616,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="13" t="s">
+      <c r="J82" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="13" t="s">
+      <c r="K82" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7646,10 +7648,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="13" t="s">
+      <c r="J83" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="13" t="s">
+      <c r="K83" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7678,10 +7680,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="13" t="s">
+      <c r="J84" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="13" t="s">
+      <c r="K84" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7710,10 +7712,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="13" t="s">
+      <c r="J85" s="14" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="13" t="s">
+      <c r="K85" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7742,10 +7744,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="13" t="s">
+      <c r="J86" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="13" t="s">
+      <c r="K86" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7774,10 +7776,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="13" t="s">
+      <c r="J87" s="14" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="13" t="s">
+      <c r="K87" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7806,10 +7808,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="13" t="s">
+      <c r="J88" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="13" t="s">
+      <c r="K88" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7838,10 +7840,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="13" t="s">
+      <c r="J89" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="13" t="s">
+      <c r="K89" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7870,10 +7872,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="13" t="s">
+      <c r="J90" s="14" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="13" t="s">
+      <c r="K90" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7902,10 +7904,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="13" t="s">
+      <c r="J91" s="14" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="13" t="s">
+      <c r="K91" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7934,10 +7936,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="13" t="s">
+      <c r="J92" s="14" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="13" t="s">
+      <c r="K92" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7966,10 +7968,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="13" t="s">
+      <c r="J93" s="14" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="13" t="s">
+      <c r="K93" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -7998,10 +8000,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="13" t="s">
+      <c r="J94" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="13" t="s">
+      <c r="K94" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -8030,10 +8032,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="13" t="s">
+      <c r="J95" s="14" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="13" t="s">
+      <c r="K95" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -8062,10 +8064,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="13" t="s">
+      <c r="J96" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="13" t="s">
+      <c r="K96" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -8094,10 +8096,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="13" t="s">
+      <c r="J97" s="14" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="13" t="s">
+      <c r="K97" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -8126,10 +8128,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="13" t="s">
+      <c r="J98" s="14" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="13" t="s">
+      <c r="K98" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -8158,10 +8160,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="13" t="s">
+      <c r="J99" s="14" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="13" t="s">
+      <c r="K99" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -8190,10 +8192,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="13" t="s">
+      <c r="J100" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="13" t="s">
+      <c r="K100" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -8222,10 +8224,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="13" t="s">
+      <c r="J101" s="14" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="13" t="s">
+      <c r="K101" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -8254,10 +8256,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="13" t="s">
+      <c r="J102" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="13" t="s">
+      <c r="K102" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -8286,10 +8288,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="13" t="s">
+      <c r="J103" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="13" t="s">
+      <c r="K103" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -8318,10 +8320,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="13" t="s">
+      <c r="J104" s="14" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="13" t="s">
+      <c r="K104" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -8350,10 +8352,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="13" t="s">
+      <c r="J105" s="14" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="13" t="s">
+      <c r="K105" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -8382,10 +8384,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="13" t="s">
+      <c r="J106" s="14" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="13" t="s">
+      <c r="K106" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8414,10 +8416,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="13" t="s">
+      <c r="J107" s="14" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="13" t="s">
+      <c r="K107" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8446,10 +8448,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="13" t="s">
+      <c r="J108" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="13" t="s">
+      <c r="K108" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8478,10 +8480,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="13" t="s">
+      <c r="J109" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="13" t="s">
+      <c r="K109" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8510,10 +8512,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="13" t="s">
+      <c r="J110" s="14" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="13" t="s">
+      <c r="K110" s="14" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8542,10 +8544,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="13" t="s">
+      <c r="J111" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="13" t="s">
+      <c r="K111" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8574,10 +8576,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="13" t="s">
+      <c r="J112" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="13" t="s">
+      <c r="K112" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8606,10 +8608,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="13" t="s">
+      <c r="J113" s="14" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="13" t="s">
+      <c r="K113" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8638,10 +8640,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="13" t="s">
+      <c r="J114" s="14" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="13" t="s">
+      <c r="K114" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8670,10 +8672,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="13" t="s">
+      <c r="J115" s="14" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="13" t="s">
+      <c r="K115" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8702,10 +8704,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="13" t="s">
+      <c r="J116" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="13" t="s">
+      <c r="K116" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8734,10 +8736,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="13" t="s">
+      <c r="J117" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="13" t="s">
+      <c r="K117" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8766,10 +8768,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="13" t="s">
+      <c r="J118" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="13" t="s">
+      <c r="K118" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8798,10 +8800,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="13" t="s">
+      <c r="J119" s="14" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="13" t="s">
+      <c r="K119" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8830,10 +8832,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="13" t="s">
+      <c r="J120" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="13" t="s">
+      <c r="K120" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8862,10 +8864,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="13" t="s">
+      <c r="J121" s="14" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="13" t="s">
+      <c r="K121" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8894,10 +8896,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="13" t="s">
+      <c r="J122" s="14" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="13" t="s">
+      <c r="K122" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8926,10 +8928,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="13" t="s">
+      <c r="J123" s="14" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K123" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8958,10 +8960,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="13" t="s">
+      <c r="J124" s="14" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="13" t="s">
+      <c r="K124" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8990,10 +8992,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="13" t="s">
+      <c r="J125" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="13" t="s">
+      <c r="K125" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -9022,10 +9024,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="13" t="s">
+      <c r="J126" s="14" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="13" t="s">
+      <c r="K126" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -9054,10 +9056,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="13" t="s">
+      <c r="J127" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K127" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -9086,10 +9088,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="13" t="s">
+      <c r="J128" s="14" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="13" t="s">
+      <c r="K128" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -9118,10 +9120,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="13" t="s">
+      <c r="J129" s="14" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="13" t="s">
+      <c r="K129" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -9150,10 +9152,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="13" t="s">
+      <c r="J130" s="14" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="13" t="s">
+      <c r="K130" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -9182,10 +9184,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="13" t="s">
+      <c r="J131" s="14" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="13" t="s">
+      <c r="K131" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -9214,10 +9216,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="13" t="s">
+      <c r="J132" s="14" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="13" t="s">
+      <c r="K132" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -9246,10 +9248,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="13" t="s">
+      <c r="J133" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="13" t="s">
+      <c r="K133" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -9278,10 +9280,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="13" t="s">
+      <c r="J134" s="14" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="13" t="s">
+      <c r="K134" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -9310,10 +9312,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="13" t="s">
+      <c r="J135" s="14" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="13" t="s">
+      <c r="K135" s="14" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -9342,10 +9344,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="13" t="s">
+      <c r="J136" s="14" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="13" t="s">
+      <c r="K136" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -9374,10 +9376,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="13" t="s">
+      <c r="J137" s="14" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="13" t="s">
+      <c r="K137" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9406,10 +9408,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="13" t="s">
+      <c r="J138" s="14" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="13" t="s">
+      <c r="K138" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9438,10 +9440,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="13" t="s">
+      <c r="J139" s="14" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="13" t="s">
+      <c r="K139" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9470,10 +9472,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="13" t="s">
+      <c r="J140" s="14" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="13" t="s">
+      <c r="K140" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9502,10 +9504,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="13" t="s">
+      <c r="J141" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="13" t="s">
+      <c r="K141" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9534,10 +9536,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="13" t="s">
+      <c r="J142" s="14" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="13" t="s">
+      <c r="K142" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9566,10 +9568,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="13" t="s">
+      <c r="J143" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="13" t="s">
+      <c r="K143" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9598,10 +9600,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="13" t="s">
+      <c r="J144" s="14" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="13" t="s">
+      <c r="K144" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9630,10 +9632,10 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="13" t="s">
+      <c r="J145" s="14" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="13" t="s">
+      <c r="K145" s="14" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
@@ -9662,13 +9664,13 @@
       <c r="I146" s="3">
         <v>0</v>
       </c>
-      <c r="J146" s="14" t="s">
+      <c r="J146" s="15" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="14" t="s">
+      <c r="K146" s="15" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="14" t="s">
+      <c r="L146" s="15" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9694,13 +9696,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="13" t="s">
+      <c r="J147" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="13" t="s">
+      <c r="K147" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="12" t="s">
+      <c r="L147" s="13" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9726,13 +9728,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="13" t="s">
+      <c r="J148" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="13" t="s">
+      <c r="K148" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="12" t="s">
+      <c r="L148" s="13" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9758,13 +9760,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="13" t="s">
+      <c r="J149" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="13" t="s">
+      <c r="K149" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="12" t="s">
+      <c r="L149" s="13" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9790,13 +9792,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="13" t="s">
+      <c r="J150" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="13" t="s">
+      <c r="K150" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="12" t="s">
+      <c r="L150" s="13" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9822,13 +9824,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="13" t="s">
+      <c r="J151" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="13" t="s">
+      <c r="K151" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="12" t="s">
+      <c r="L151" s="13" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9854,13 +9856,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="13" t="s">
+      <c r="J152" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="13" t="s">
+      <c r="K152" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="12" t="s">
+      <c r="L152" s="13" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9886,13 +9888,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="13" t="s">
+      <c r="J153" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="13" t="s">
+      <c r="K153" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="12" t="s">
+      <c r="L153" s="13" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9918,13 +9920,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="13" t="s">
+      <c r="J154" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="13" t="s">
+      <c r="K154" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="12" t="s">
+      <c r="L154" s="13" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9950,13 +9952,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="13" t="s">
+      <c r="J155" s="14" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="13" t="s">
+      <c r="K155" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="12" t="s">
+      <c r="L155" s="13" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9982,13 +9984,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="13" t="s">
+      <c r="J156" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="13" t="s">
+      <c r="K156" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="12" t="s">
+      <c r="L156" s="13" t="s">
         <v>889</v>
       </c>
     </row>
@@ -10014,13 +10016,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="13" t="s">
+      <c r="J157" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="13" t="s">
+      <c r="K157" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="12" t="s">
+      <c r="L157" s="13" t="s">
         <v>894</v>
       </c>
     </row>
@@ -10046,13 +10048,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="13" t="s">
+      <c r="J158" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="13" t="s">
+      <c r="K158" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="12" t="s">
+      <c r="L158" s="13" t="s">
         <v>899</v>
       </c>
     </row>
@@ -10078,13 +10080,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="13" t="s">
+      <c r="J159" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="13" t="s">
+      <c r="K159" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="12" t="s">
+      <c r="L159" s="13" t="s">
         <v>904</v>
       </c>
     </row>
@@ -10110,13 +10112,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="13" t="s">
+      <c r="J160" s="14" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="13" t="s">
+      <c r="K160" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="12" t="s">
+      <c r="L160" s="13" t="s">
         <v>909</v>
       </c>
     </row>
@@ -10142,13 +10144,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="13" t="s">
+      <c r="J161" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="13" t="s">
+      <c r="K161" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="12" t="s">
+      <c r="L161" s="13" t="s">
         <v>915</v>
       </c>
     </row>
@@ -10174,13 +10176,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="13" t="s">
+      <c r="J162" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="13" t="s">
+      <c r="K162" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="12" t="s">
+      <c r="L162" s="13" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10206,13 +10208,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="13" t="s">
+      <c r="J163" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="13" t="s">
+      <c r="K163" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="12" t="s">
+      <c r="L163" s="13" t="s">
         <v>925</v>
       </c>
     </row>
@@ -10238,13 +10240,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="13" t="s">
+      <c r="J164" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="13" t="s">
+      <c r="K164" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="12" t="s">
+      <c r="L164" s="13" t="s">
         <v>930</v>
       </c>
     </row>
@@ -10270,13 +10272,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="13" t="s">
+      <c r="J165" s="14" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="13" t="s">
+      <c r="K165" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="12" t="s">
+      <c r="L165" s="13" t="s">
         <v>935</v>
       </c>
     </row>
@@ -10302,13 +10304,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="13" t="s">
+      <c r="J166" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="13" t="s">
+      <c r="K166" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="12" t="s">
+      <c r="L166" s="13" t="s">
         <v>941</v>
       </c>
     </row>
@@ -10334,13 +10336,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="13" t="s">
+      <c r="J167" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="13" t="s">
+      <c r="K167" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="12" t="s">
+      <c r="L167" s="13" t="s">
         <v>946</v>
       </c>
     </row>
@@ -10366,13 +10368,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="13" t="s">
+      <c r="J168" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="13" t="s">
+      <c r="K168" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="12" t="s">
+      <c r="L168" s="13" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10398,13 +10400,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="13" t="s">
+      <c r="J169" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="13" t="s">
+      <c r="K169" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="12" t="s">
+      <c r="L169" s="13" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10430,13 +10432,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="13" t="s">
+      <c r="J170" s="14" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="13" t="s">
+      <c r="K170" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="12" t="s">
+      <c r="L170" s="13" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10462,13 +10464,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="13" t="s">
+      <c r="J171" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="13" t="s">
+      <c r="K171" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="12" t="s">
+      <c r="L171" s="13" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10494,13 +10496,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="13" t="s">
+      <c r="J172" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="13" t="s">
+      <c r="K172" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="12" t="s">
+      <c r="L172" s="13" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10526,13 +10528,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="13" t="s">
+      <c r="J173" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="13" t="s">
+      <c r="K173" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="12" t="s">
+      <c r="L173" s="13" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10558,13 +10560,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="13" t="s">
+      <c r="J174" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="13" t="s">
+      <c r="K174" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="12" t="s">
+      <c r="L174" s="13" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10590,13 +10592,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="13" t="s">
+      <c r="J175" s="14" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="13" t="s">
+      <c r="K175" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="12" t="s">
+      <c r="L175" s="13" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10622,13 +10624,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="13" t="s">
+      <c r="J176" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="13" t="s">
+      <c r="K176" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="12" t="s">
+      <c r="L176" s="13" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10654,13 +10656,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="13" t="s">
+      <c r="J177" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="13" t="s">
+      <c r="K177" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="12" t="s">
+      <c r="L177" s="13" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10686,13 +10688,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="13" t="s">
+      <c r="J178" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="13" t="s">
+      <c r="K178" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="12" t="s">
+      <c r="L178" s="13" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10718,13 +10720,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="13" t="s">
+      <c r="J179" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="13" t="s">
+      <c r="K179" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="12" t="s">
+      <c r="L179" s="13" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10750,13 +10752,13 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="13" t="s">
+      <c r="J180" s="14" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="13" t="s">
+      <c r="K180" s="14" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="12" t="s">
+      <c r="L180" s="13" t="s">
         <v>1014</v>
       </c>
     </row>
@@ -10782,13 +10784,13 @@
       <c r="I181" s="3">
         <v>0</v>
       </c>
-      <c r="J181" s="14" t="s">
+      <c r="J181" s="15" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="14" t="s">
+      <c r="K181" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="12" t="s">
+      <c r="L181" s="13" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10814,13 +10816,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="13" t="s">
+      <c r="J182" s="14" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="13" t="s">
+      <c r="K182" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="12" t="s">
+      <c r="L182" s="13" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10846,13 +10848,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="13" t="s">
+      <c r="J183" s="14" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="13" t="s">
+      <c r="K183" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="12" t="s">
+      <c r="L183" s="13" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10878,13 +10880,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="13" t="s">
+      <c r="J184" s="14" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="13" t="s">
+      <c r="K184" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="12" t="s">
+      <c r="L184" s="13" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10910,13 +10912,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="13" t="s">
+      <c r="J185" s="14" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="13" t="s">
+      <c r="K185" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="12" t="s">
+      <c r="L185" s="13" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10942,13 +10944,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="13" t="s">
+      <c r="J186" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="13" t="s">
+      <c r="K186" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="12" t="s">
+      <c r="L186" s="13" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10974,13 +10976,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="13" t="s">
+      <c r="J187" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="13" t="s">
+      <c r="K187" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="12" t="s">
+      <c r="L187" s="13" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -11006,13 +11008,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="13" t="s">
+      <c r="J188" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="13" t="s">
+      <c r="K188" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="12" t="s">
+      <c r="L188" s="13" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -11038,13 +11040,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="13" t="s">
+      <c r="J189" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="13" t="s">
+      <c r="K189" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="12" t="s">
+      <c r="L189" s="13" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -11070,13 +11072,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="13" t="s">
+      <c r="J190" s="14" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="13" t="s">
+      <c r="K190" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="12" t="s">
+      <c r="L190" s="13" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -11102,13 +11104,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="13" t="s">
+      <c r="J191" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="13" t="s">
+      <c r="K191" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="12" t="s">
+      <c r="L191" s="13" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -11134,13 +11136,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="13" t="s">
+      <c r="J192" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="13" t="s">
+      <c r="K192" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="12" t="s">
+      <c r="L192" s="13" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -11166,13 +11168,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="13" t="s">
+      <c r="J193" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="13" t="s">
+      <c r="K193" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="12" t="s">
+      <c r="L193" s="13" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -11198,13 +11200,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="13" t="s">
+      <c r="J194" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="13" t="s">
+      <c r="K194" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="12" t="s">
+      <c r="L194" s="13" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -11230,13 +11232,13 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="13" t="s">
+      <c r="J195" s="14" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="13" t="s">
+      <c r="K195" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="12" t="s">
+      <c r="L195" s="13" t="s">
         <v>1097</v>
       </c>
     </row>
@@ -11262,13 +11264,13 @@
       <c r="I196" s="4">
         <v>0</v>
       </c>
-      <c r="J196" s="15" t="s">
+      <c r="J196" s="16" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="15" t="s">
+      <c r="K196" s="16" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="15" t="s">
+      <c r="L196" s="16" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -11294,13 +11296,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="13" t="s">
+      <c r="J197" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="13" t="s">
+      <c r="K197" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="12" t="s">
+      <c r="L197" s="13" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -11326,13 +11328,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="13" t="s">
+      <c r="J198" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="13" t="s">
+      <c r="K198" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="12" t="s">
+      <c r="L198" s="13" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -11358,13 +11360,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="13" t="s">
+      <c r="J199" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="13" t="s">
+      <c r="K199" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="12" t="s">
+      <c r="L199" s="13" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11390,13 +11392,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="13" t="s">
+      <c r="J200" s="14" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="13" t="s">
+      <c r="K200" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="12" t="s">
+      <c r="L200" s="13" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11422,13 +11424,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="13" t="s">
+      <c r="J201" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="13" t="s">
+      <c r="K201" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="12" t="s">
+      <c r="L201" s="13" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11454,13 +11456,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="13" t="s">
+      <c r="J202" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="13" t="s">
+      <c r="K202" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="12" t="s">
+      <c r="L202" s="13" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11486,13 +11488,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="13" t="s">
+      <c r="J203" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="13" t="s">
+      <c r="K203" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="12" t="s">
+      <c r="L203" s="13" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11518,13 +11520,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="13" t="s">
+      <c r="J204" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="13" t="s">
+      <c r="K204" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="12" t="s">
+      <c r="L204" s="13" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11550,13 +11552,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="13" t="s">
+      <c r="J205" s="14" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="13" t="s">
+      <c r="K205" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="12" t="s">
+      <c r="L205" s="13" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11582,13 +11584,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="13" t="s">
+      <c r="J206" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="13" t="s">
+      <c r="K206" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="12" t="s">
+      <c r="L206" s="13" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11614,13 +11616,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="13" t="s">
+      <c r="J207" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="13" t="s">
+      <c r="K207" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="12" t="s">
+      <c r="L207" s="13" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11646,13 +11648,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="13" t="s">
+      <c r="J208" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="13" t="s">
+      <c r="K208" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="12" t="s">
+      <c r="L208" s="13" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11678,13 +11680,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="13" t="s">
+      <c r="J209" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="13" t="s">
+      <c r="K209" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="12" t="s">
+      <c r="L209" s="13" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11710,13 +11712,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="13" t="s">
+      <c r="J210" s="14" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="13" t="s">
+      <c r="K210" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="12" t="s">
+      <c r="L210" s="13" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11742,13 +11744,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="13" t="s">
+      <c r="J211" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="13" t="s">
+      <c r="K211" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="12" t="s">
+      <c r="L211" s="13" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11774,13 +11776,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="13" t="s">
+      <c r="J212" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="13" t="s">
+      <c r="K212" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="12" t="s">
+      <c r="L212" s="13" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11806,13 +11808,13 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="13" t="s">
+      <c r="J213" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="13" t="s">
+      <c r="K213" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="12" t="s">
+      <c r="L213" s="13" t="s">
         <v>1191</v>
       </c>
     </row>
@@ -11840,13 +11842,13 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="13" t="s">
+      <c r="J214" s="14" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="13" t="s">
+      <c r="K214" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="12" t="s">
+      <c r="L214" s="13" t="s">
         <v>1196</v>
       </c>
     </row>
@@ -11874,13 +11876,13 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="13" t="s">
+      <c r="J215" s="14" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="13" t="s">
+      <c r="K215" s="14" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="12" t="s">
+      <c r="L215" s="13" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -11908,13 +11910,13 @@
       <c r="I216" s="3">
         <v>0</v>
       </c>
-      <c r="J216" s="14" t="s">
+      <c r="J216" s="15" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="14" t="s">
+      <c r="K216" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="12" t="s">
+      <c r="L216" s="13" t="s">
         <v>1209</v>
       </c>
       <c r="M216" s="3" t="s">
@@ -11945,13 +11947,13 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="13" t="s">
+      <c r="J217" s="14" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="13" t="s">
+      <c r="K217" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="12" t="s">
+      <c r="L217" s="13" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -11979,13 +11981,13 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="13" t="s">
+      <c r="J218" s="14" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="13" t="s">
+      <c r="K218" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="12" t="s">
+      <c r="L218" s="13" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -12013,13 +12015,13 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="13" t="s">
+      <c r="J219" s="14" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="13" t="s">
+      <c r="K219" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="12" t="s">
+      <c r="L219" s="13" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -12047,13 +12049,13 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="13" t="s">
+      <c r="J220" s="14" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="13" t="s">
+      <c r="K220" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="12" t="s">
+      <c r="L220" s="13" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -12081,13 +12083,13 @@
       <c r="I221" s="3">
         <v>0</v>
       </c>
-      <c r="J221" s="13" t="s">
+      <c r="J221" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="K221" s="14" t="s">
+      <c r="K221" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L221" s="12" t="s">
+      <c r="L221" s="13" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -12113,13 +12115,13 @@
       <c r="I222" s="1">
         <v>0</v>
       </c>
-      <c r="J222" s="13" t="s">
+      <c r="J222" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="K222" s="13" t="s">
+      <c r="K222" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L222" s="12" t="s">
+      <c r="L222" s="13" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -12145,13 +12147,13 @@
       <c r="I223" s="1">
         <v>0</v>
       </c>
-      <c r="J223" s="13" t="s">
+      <c r="J223" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="K223" s="13" t="s">
+      <c r="K223" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L223" s="12" t="s">
+      <c r="L223" s="13" t="s">
         <v>1243</v>
       </c>
     </row>
@@ -12177,13 +12179,13 @@
       <c r="I224" s="1">
         <v>0</v>
       </c>
-      <c r="J224" s="13" t="s">
+      <c r="J224" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="K224" s="13" t="s">
+      <c r="K224" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L224" s="12" t="s">
+      <c r="L224" s="13" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -12209,13 +12211,13 @@
       <c r="I225" s="1">
         <v>0</v>
       </c>
-      <c r="J225" s="13" t="s">
+      <c r="J225" s="14" t="s">
         <v>1234</v>
       </c>
-      <c r="K225" s="13" t="s">
+      <c r="K225" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L225" s="12" t="s">
+      <c r="L225" s="13" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -12241,13 +12243,13 @@
       <c r="I226" s="3">
         <v>0</v>
       </c>
-      <c r="J226" s="13" t="s">
+      <c r="J226" s="14" t="s">
         <v>1255</v>
       </c>
-      <c r="K226" s="14" t="s">
+      <c r="K226" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L226" s="12" t="s">
+      <c r="L226" s="13" t="s">
         <v>1256</v>
       </c>
     </row>
@@ -12273,13 +12275,13 @@
       <c r="I227" s="1">
         <v>0</v>
       </c>
-      <c r="J227" s="13" t="s">
+      <c r="J227" s="14" t="s">
         <v>1255</v>
       </c>
-      <c r="K227" s="13" t="s">
+      <c r="K227" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L227" s="12" t="s">
+      <c r="L227" s="13" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -12305,13 +12307,13 @@
       <c r="I228" s="1">
         <v>0</v>
       </c>
-      <c r="J228" s="13" t="s">
+      <c r="J228" s="14" t="s">
         <v>1255</v>
       </c>
-      <c r="K228" s="13" t="s">
+      <c r="K228" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L228" s="12" t="s">
+      <c r="L228" s="13" t="s">
         <v>1264</v>
       </c>
     </row>
@@ -12337,13 +12339,13 @@
       <c r="I229" s="1">
         <v>0</v>
       </c>
-      <c r="J229" s="13" t="s">
+      <c r="J229" s="14" t="s">
         <v>1255</v>
       </c>
-      <c r="K229" s="13" t="s">
+      <c r="K229" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L229" s="12" t="s">
+      <c r="L229" s="13" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -12369,13 +12371,13 @@
       <c r="I230" s="1">
         <v>0</v>
       </c>
-      <c r="J230" s="13" t="s">
+      <c r="J230" s="14" t="s">
         <v>1255</v>
       </c>
-      <c r="K230" s="13" t="s">
+      <c r="K230" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L230" s="12" t="s">
+      <c r="L230" s="13" t="s">
         <v>1272</v>
       </c>
     </row>
@@ -12401,13 +12403,13 @@
       <c r="I231" s="3">
         <v>0</v>
       </c>
-      <c r="J231" s="13" t="s">
+      <c r="J231" s="14" t="s">
         <v>1276</v>
       </c>
-      <c r="K231" s="14" t="s">
+      <c r="K231" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L231" s="12" t="s">
+      <c r="L231" s="13" t="s">
         <v>1277</v>
       </c>
     </row>
@@ -12433,13 +12435,13 @@
       <c r="I232" s="1">
         <v>0</v>
       </c>
-      <c r="J232" s="13" t="s">
+      <c r="J232" s="14" t="s">
         <v>1276</v>
       </c>
-      <c r="K232" s="13" t="s">
+      <c r="K232" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L232" s="12" t="s">
+      <c r="L232" s="13" t="s">
         <v>1281</v>
       </c>
     </row>
@@ -12465,13 +12467,13 @@
       <c r="I233" s="1">
         <v>0</v>
       </c>
-      <c r="J233" s="13" t="s">
+      <c r="J233" s="14" t="s">
         <v>1276</v>
       </c>
-      <c r="K233" s="13" t="s">
+      <c r="K233" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L233" s="12" t="s">
+      <c r="L233" s="13" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -12497,13 +12499,13 @@
       <c r="I234" s="1">
         <v>0</v>
       </c>
-      <c r="J234" s="13" t="s">
+      <c r="J234" s="14" t="s">
         <v>1276</v>
       </c>
-      <c r="K234" s="13" t="s">
+      <c r="K234" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L234" s="12" t="s">
+      <c r="L234" s="13" t="s">
         <v>1289</v>
       </c>
     </row>
@@ -12529,13 +12531,13 @@
       <c r="I235" s="1">
         <v>0</v>
       </c>
-      <c r="J235" s="13" t="s">
+      <c r="J235" s="14" t="s">
         <v>1276</v>
       </c>
-      <c r="K235" s="13" t="s">
+      <c r="K235" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L235" s="12" t="s">
+      <c r="L235" s="13" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -12561,13 +12563,13 @@
       <c r="I236" s="3">
         <v>0</v>
       </c>
-      <c r="J236" s="13" t="s">
+      <c r="J236" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="K236" s="14" t="s">
+      <c r="K236" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L236" s="12" t="s">
+      <c r="L236" s="13" t="s">
         <v>1298</v>
       </c>
     </row>
@@ -12593,13 +12595,13 @@
       <c r="I237" s="1">
         <v>0</v>
       </c>
-      <c r="J237" s="13" t="s">
+      <c r="J237" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="K237" s="13" t="s">
+      <c r="K237" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L237" s="12" t="s">
+      <c r="L237" s="13" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -12625,13 +12627,13 @@
       <c r="I238" s="1">
         <v>0</v>
       </c>
-      <c r="J238" s="13" t="s">
+      <c r="J238" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="K238" s="13" t="s">
+      <c r="K238" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L238" s="12" t="s">
+      <c r="L238" s="13" t="s">
         <v>1306</v>
       </c>
     </row>
@@ -12657,13 +12659,13 @@
       <c r="I239" s="1">
         <v>0</v>
       </c>
-      <c r="J239" s="13" t="s">
+      <c r="J239" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="K239" s="13" t="s">
+      <c r="K239" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L239" s="12" t="s">
+      <c r="L239" s="13" t="s">
         <v>1310</v>
       </c>
     </row>
@@ -12689,17 +12691,17 @@
       <c r="I240" s="1">
         <v>0</v>
       </c>
-      <c r="J240" s="13" t="s">
+      <c r="J240" s="14" t="s">
         <v>1297</v>
       </c>
-      <c r="K240" s="13" t="s">
+      <c r="K240" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L240" s="12" t="s">
+      <c r="L240" s="13" t="s">
         <v>1314</v>
       </c>
     </row>
-    <row r="241" customHeight="1" spans="1:12">
+    <row r="241" customHeight="1" spans="3:12">
       <c r="C241" s="1">
         <v>1235</v>
       </c>
@@ -12721,17 +12723,17 @@
       <c r="I241" s="3">
         <v>0</v>
       </c>
-      <c r="J241" s="13" t="s">
+      <c r="J241" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="K241" s="14" t="s">
+      <c r="K241" s="15" t="s">
         <v>1208</v>
       </c>
-      <c r="L241" s="12" t="s">
+      <c r="L241" s="13" t="s">
         <v>1319</v>
       </c>
     </row>
-    <row r="242" customHeight="1" spans="1:12">
+    <row r="242" customHeight="1" spans="3:12">
       <c r="C242" s="1">
         <v>1236</v>
       </c>
@@ -12753,17 +12755,17 @@
       <c r="I242" s="1">
         <v>0</v>
       </c>
-      <c r="J242" s="13" t="s">
+      <c r="J242" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="K242" s="13" t="s">
+      <c r="K242" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L242" s="12" t="s">
+      <c r="L242" s="13" t="s">
         <v>1323</v>
       </c>
     </row>
-    <row r="243" customHeight="1" spans="1:12">
+    <row r="243" customHeight="1" spans="3:12">
       <c r="C243" s="1">
         <v>1237</v>
       </c>
@@ -12785,17 +12787,17 @@
       <c r="I243" s="1">
         <v>0</v>
       </c>
-      <c r="J243" s="13" t="s">
+      <c r="J243" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="K243" s="13" t="s">
+      <c r="K243" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L243" s="12" t="s">
+      <c r="L243" s="13" t="s">
         <v>1327</v>
       </c>
     </row>
-    <row r="244" customHeight="1" spans="1:12">
+    <row r="244" customHeight="1" spans="3:12">
       <c r="C244" s="1">
         <v>1238</v>
       </c>
@@ -12817,17 +12819,17 @@
       <c r="I244" s="1">
         <v>0</v>
       </c>
-      <c r="J244" s="13" t="s">
+      <c r="J244" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="K244" s="13" t="s">
+      <c r="K244" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L244" s="12" t="s">
+      <c r="L244" s="13" t="s">
         <v>1331</v>
       </c>
     </row>
-    <row r="245" customHeight="1" spans="1:12">
+    <row r="245" customHeight="1" spans="3:12">
       <c r="C245" s="1">
         <v>1239</v>
       </c>
@@ -12849,28 +12851,22 @@
       <c r="I245" s="1">
         <v>0</v>
       </c>
-      <c r="J245" s="13" t="s">
+      <c r="J245" s="14" t="s">
         <v>1318</v>
       </c>
-      <c r="K245" s="13" t="s">
+      <c r="K245" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L245" s="12" t="s">
+      <c r="L245" s="13" t="s">
         <v>1335</v>
       </c>
     </row>
-    <row r="246" customHeight="1" spans="1:12">
-      <c r="A246" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B246" s="1" t="s">
-        <v>1336</v>
-      </c>
+    <row r="246" customHeight="1" spans="3:12">
       <c r="C246" s="1">
         <v>1240</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E246" s="2">
         <v>6</v>
@@ -12879,31 +12875,25 @@
         <v>6</v>
       </c>
       <c r="G246" s="11" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H246" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="H246" s="1" t="s">
+      <c r="I246" s="3">
+        <v>0</v>
+      </c>
+      <c r="J246" s="14" t="s">
         <v>1339</v>
       </c>
-      <c r="I246" s="3">
-        <v>0</v>
-      </c>
-      <c r="J246" s="13" t="s">
+      <c r="K246" s="15" t="s">
         <v>1340</v>
       </c>
-      <c r="K246" s="14" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L246" s="12" t="s">
+      <c r="L246" s="13" t="s">
         <v>1341</v>
       </c>
     </row>
-    <row r="247" customHeight="1" spans="1:12">
-      <c r="A247" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B247" s="1" t="s">
-        <v>1336</v>
-      </c>
+    <row r="247" customHeight="1" spans="3:12">
       <c r="C247" s="1">
         <v>1241</v>
       </c>
@@ -12925,23 +12915,17 @@
       <c r="I247" s="1">
         <v>0</v>
       </c>
-      <c r="J247" s="13" t="s">
+      <c r="J247" s="14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K247" s="17" t="s">
         <v>1340</v>
       </c>
-      <c r="K247" s="13" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L247" s="12" t="s">
+      <c r="L247" s="13" t="s">
         <v>1345</v>
       </c>
     </row>
-    <row r="248" customHeight="1" spans="1:12">
-      <c r="A248" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>1336</v>
-      </c>
+    <row r="248" customHeight="1" spans="3:12">
       <c r="C248" s="1">
         <v>1242</v>
       </c>
@@ -12963,23 +12947,17 @@
       <c r="I248" s="1">
         <v>0</v>
       </c>
-      <c r="J248" s="13" t="s">
+      <c r="J248" s="14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K248" s="17" t="s">
         <v>1340</v>
       </c>
-      <c r="K248" s="13" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L248" s="12" t="s">
+      <c r="L248" s="13" t="s">
         <v>1349</v>
       </c>
     </row>
-    <row r="249" customHeight="1" spans="1:12">
-      <c r="A249" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>1336</v>
-      </c>
+    <row r="249" customHeight="1" spans="3:12">
       <c r="C249" s="1">
         <v>1243</v>
       </c>
@@ -13001,23 +12979,17 @@
       <c r="I249" s="1">
         <v>0</v>
       </c>
-      <c r="J249" s="13" t="s">
+      <c r="J249" s="14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K249" s="17" t="s">
         <v>1340</v>
       </c>
-      <c r="K249" s="13" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L249" s="12" t="s">
+      <c r="L249" s="13" t="s">
         <v>1353</v>
       </c>
     </row>
-    <row r="250" customHeight="1" spans="1:12">
-      <c r="A250" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>1336</v>
-      </c>
+    <row r="250" customHeight="1" spans="3:12">
       <c r="C250" s="1">
         <v>1244</v>
       </c>
@@ -13039,13 +13011,13 @@
       <c r="I250" s="1">
         <v>0</v>
       </c>
-      <c r="J250" s="13" t="s">
+      <c r="J250" s="14" t="s">
+        <v>1339</v>
+      </c>
+      <c r="K250" s="17" t="s">
         <v>1340</v>
       </c>
-      <c r="K250" s="13" t="s">
-        <v>1208</v>
-      </c>
-      <c r="L250" s="12" t="s">
+      <c r="L250" s="13" t="s">
         <v>1357</v>
       </c>
     </row>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4083,10 +4083,10 @@
     <t>虚无战锤，35升阶石</t>
   </si>
   <si>
-    <t>202002,106,504,210090,1009,506,202008,202003,507,508</t>
-  </si>
-  <si>
-    <t>10,18000,98000,600000,140000,900000,1200000,1000000,1000000,2000000</t>
+    <t>202002,106,504,210090,1009,202008,202003,507,508</t>
+  </si>
+  <si>
+    <t>10,18000,98000,600000,140000,1200000,1000000,1000000,2000000</t>
   </si>
   <si>
     <t>10240</t>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="1477">
   <si>
     <t>_Id</t>
   </si>
@@ -4138,6 +4139,363 @@
   </si>
   <si>
     <t>10244</t>
+  </si>
+  <si>
+    <t>寂灭小村</t>
+  </si>
+  <si>
+    <t>寂灭装备，36升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210091,1009,202014,202008,507,508</t>
+  </si>
+  <si>
+    <t>10,18000,98000,600000,140000,1200000,1000000,2000000,2000000</t>
+  </si>
+  <si>
+    <t>10245</t>
+  </si>
+  <si>
+    <t>基础装备，四格，基础专属，生阶石，口粮，虚无装备，寂灭装备，永恒专属,虚无专属</t>
+  </si>
+  <si>
+    <t>寂灭村外</t>
+  </si>
+  <si>
+    <t>寂灭鹿茸，36升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210091,1009,202015,202008,507,508</t>
+  </si>
+  <si>
+    <t>10246</t>
+  </si>
+  <si>
+    <t>寂灭农场</t>
+  </si>
+  <si>
+    <t>寂灭草帽，36升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210091,1009,202016,202008,507,508</t>
+  </si>
+  <si>
+    <t>10247</t>
+  </si>
+  <si>
+    <t>寂灭老城</t>
+  </si>
+  <si>
+    <t>寂灭猫爪，36升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210091,1009,202017,202008,507,508</t>
+  </si>
+  <si>
+    <t>10248</t>
+  </si>
+  <si>
+    <t>寂灭森林</t>
+  </si>
+  <si>
+    <t>寂灭花朵，36升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210091,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10249</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>寂灭蝠洞</t>
+  </si>
+  <si>
+    <t>寂灭冰晶，37升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210092,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10250</t>
+  </si>
+  <si>
+    <t>寂灭骷髅洞</t>
+  </si>
+  <si>
+    <t>寂灭蝠翼，37升阶石</t>
+  </si>
+  <si>
+    <t>10251</t>
+  </si>
+  <si>
+    <t>寂灭通道</t>
+  </si>
+  <si>
+    <t>寂灭魂火，37升阶石</t>
+  </si>
+  <si>
+    <t>10252</t>
+  </si>
+  <si>
+    <t>寂灭尸洞</t>
+  </si>
+  <si>
+    <t>寂灭腐肉，37升阶石</t>
+  </si>
+  <si>
+    <t>10253</t>
+  </si>
+  <si>
+    <t>寂灭蛇谷</t>
+  </si>
+  <si>
+    <t>寂灭蛇胆，37升阶石</t>
+  </si>
+  <si>
+    <t>10254</t>
+  </si>
+  <si>
+    <t>寂灭狼山</t>
+  </si>
+  <si>
+    <t>寂灭狼爪，38升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210093,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10255</t>
+  </si>
+  <si>
+    <t>寂灭沙洞</t>
+  </si>
+  <si>
+    <t>寂灭虫皮，38升阶石</t>
+  </si>
+  <si>
+    <t>10256</t>
+  </si>
+  <si>
+    <t>寂灭鹰崖</t>
+  </si>
+  <si>
+    <t>寂灭鹰羽，38升阶石</t>
+  </si>
+  <si>
+    <t>10257</t>
+  </si>
+  <si>
+    <t>寂灭虫谷</t>
+  </si>
+  <si>
+    <t>寂灭虫角，38升阶石</t>
+  </si>
+  <si>
+    <t>10258</t>
+  </si>
+  <si>
+    <t>寂灭虫洞</t>
+  </si>
+  <si>
+    <t>寂灭蜈膏，38升阶石</t>
+  </si>
+  <si>
+    <t>10259</t>
+  </si>
+  <si>
+    <t>寂灭虫穴</t>
+  </si>
+  <si>
+    <t>寂灭虫心，39升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210094,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10260</t>
+  </si>
+  <si>
+    <t>寂灭虫巢</t>
+  </si>
+  <si>
+    <t>寂灭龙皮，39升阶石</t>
+  </si>
+  <si>
+    <t>10261</t>
+  </si>
+  <si>
+    <t>寂灭魔猪厅</t>
+  </si>
+  <si>
+    <t>寂灭猪皮，39升阶石</t>
+  </si>
+  <si>
+    <t>10262</t>
+  </si>
+  <si>
+    <t>寂灭魔猪殿</t>
+  </si>
+  <si>
+    <t>寂灭猪心，39升阶石</t>
+  </si>
+  <si>
+    <t>10263</t>
+  </si>
+  <si>
+    <t>寂灭桃源</t>
+  </si>
+  <si>
+    <t>寂灭蝎皮，39升阶石</t>
+  </si>
+  <si>
+    <t>10264</t>
+  </si>
+  <si>
+    <t>寂灭魔禁地</t>
+  </si>
+  <si>
+    <t>寂灭宝甲，40升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210095,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10265</t>
+  </si>
+  <si>
+    <t>寂灭魔神殿</t>
+  </si>
+  <si>
+    <t>寂灭号角，40升阶石</t>
+  </si>
+  <si>
+    <t>10266</t>
+  </si>
+  <si>
+    <t>寂灭邪禁地</t>
+  </si>
+  <si>
+    <t>寂灭雕像，40升阶石</t>
+  </si>
+  <si>
+    <t>10267</t>
+  </si>
+  <si>
+    <t>寂灭邪魔殿</t>
+  </si>
+  <si>
+    <t>寂灭神像，40升阶石</t>
+  </si>
+  <si>
+    <t>10268</t>
+  </si>
+  <si>
+    <t>寂灭封魔殿</t>
+  </si>
+  <si>
+    <t>寂灭獠牙，40升阶石</t>
+  </si>
+  <si>
+    <t>10269</t>
+  </si>
+  <si>
+    <t>寂灭烈焰殿</t>
+  </si>
+  <si>
+    <t>寂灭树心，41升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210096,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10270</t>
+  </si>
+  <si>
+    <t>寂灭封邪殿</t>
+  </si>
+  <si>
+    <t>寂灭魔心，41升阶石</t>
+  </si>
+  <si>
+    <t>10271</t>
+  </si>
+  <si>
+    <t>寂灭尸魔殿</t>
+  </si>
+  <si>
+    <t>寂灭尸心，41升阶石</t>
+  </si>
+  <si>
+    <t>10272</t>
+  </si>
+  <si>
+    <t>寂灭骨魔殿</t>
+  </si>
+  <si>
+    <t>寂灭法杖，41升阶石</t>
+  </si>
+  <si>
+    <t>10273</t>
+  </si>
+  <si>
+    <t>寂灭魔牛殿</t>
+  </si>
+  <si>
+    <t>寂灭权杖，41升阶石</t>
+  </si>
+  <si>
+    <t>10274</t>
+  </si>
+  <si>
+    <t>寂灭水龙谷</t>
+  </si>
+  <si>
+    <t>寂灭战锤，42升阶石</t>
+  </si>
+  <si>
+    <t>202002,107,504,210097,1009,202013,202008,507,508</t>
+  </si>
+  <si>
+    <t>10275</t>
+  </si>
+  <si>
+    <t>寂灭土龙谷</t>
+  </si>
+  <si>
+    <t>寂灭血核，42升阶石</t>
+  </si>
+  <si>
+    <t>10276</t>
+  </si>
+  <si>
+    <t>寂灭毒龙谷</t>
+  </si>
+  <si>
+    <t>寂灭魔核，42升阶石</t>
+  </si>
+  <si>
+    <t>10277</t>
+  </si>
+  <si>
+    <t>寂灭火龙谷</t>
+  </si>
+  <si>
+    <t>寂灭龙甲，42升阶石</t>
+  </si>
+  <si>
+    <t>10278</t>
+  </si>
+  <si>
+    <t>寂灭冰龙谷</t>
+  </si>
+  <si>
+    <t>寂灭龙爪，42升阶石</t>
+  </si>
+  <si>
+    <t>10279</t>
   </si>
 </sst>
 </file>
@@ -4316,12 +4674,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4787,29 +5145,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5176,109 +5532,109 @@
     <col min="9" max="9" width="11.6272727272727" style="1" customWidth="1"/>
     <col min="10" max="10" width="61.0909090909091" style="1" customWidth="1"/>
     <col min="11" max="11" width="62.8181818181818" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5454545454545" style="5" customWidth="1"/>
+    <col min="12" max="12" width="12.5454545454545" style="10" customWidth="1"/>
     <col min="13" max="13" width="57.4545454545455" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9.25454545454545" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:13">
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="3"/>
     </row>
     <row r="4" customHeight="1" spans="3:13">
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="3"/>
     </row>
     <row r="5" customHeight="1" spans="3:13">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="3"/>
     </row>
     <row r="6" customHeight="1" spans="3:13">
       <c r="C6" s="1" t="s">
@@ -6483,10 +6839,10 @@
       <c r="I46" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J46" s="13" t="s">
+      <c r="J46" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="K46" s="13" t="s">
+      <c r="K46" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L46" s="1" t="s">
@@ -6512,10 +6868,10 @@
       <c r="I47" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J47" s="13" t="s">
+      <c r="J47" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="K47" s="13" t="s">
+      <c r="K47" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L47" s="1" t="s">
@@ -6541,10 +6897,10 @@
       <c r="I48" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="J48" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K48" s="13" t="s">
+      <c r="K48" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L48" s="1" t="s">
@@ -6570,10 +6926,10 @@
       <c r="I49" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="J49" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="K49" s="13" t="s">
+      <c r="K49" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L49" s="1" t="s">
@@ -6599,10 +6955,10 @@
       <c r="I50" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="J50" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="K50" s="13" t="s">
+      <c r="K50" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L50" s="1" t="s">
@@ -6631,10 +6987,10 @@
       <c r="I51" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="J51" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="K51" s="13" t="s">
+      <c r="K51" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L51" s="1" t="s">
@@ -6660,10 +7016,10 @@
       <c r="I52" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J52" s="13" t="s">
+      <c r="J52" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="K52" s="13" t="s">
+      <c r="K52" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L52" s="1" t="s">
@@ -6689,10 +7045,10 @@
       <c r="I53" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J53" s="13" t="s">
+      <c r="J53" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="K53" s="13" t="s">
+      <c r="K53" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L53" s="1" t="s">
@@ -6718,10 +7074,10 @@
       <c r="I54" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="J54" s="13" t="s">
+      <c r="J54" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="K54" s="13" t="s">
+      <c r="K54" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L54" s="1" t="s">
@@ -6747,10 +7103,10 @@
       <c r="I55" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="J55" s="13" t="s">
+      <c r="J55" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="K55" s="13" t="s">
+      <c r="K55" s="12" t="s">
         <v>264</v>
       </c>
       <c r="L55" s="1" t="s">
@@ -6779,10 +7135,10 @@
       <c r="I56" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J56" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="K56" s="13" t="s">
+      <c r="K56" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L56" s="1" t="s">
@@ -6811,10 +7167,10 @@
       <c r="I57" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="J57" s="13" t="s">
+      <c r="J57" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="K57" s="13" t="s">
+      <c r="K57" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L57" s="1" t="s">
@@ -6843,10 +7199,10 @@
       <c r="I58" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J58" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K58" s="13" t="s">
+      <c r="K58" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L58" s="1" t="s">
@@ -6875,10 +7231,10 @@
       <c r="I59" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="J59" s="13" t="s">
+      <c r="J59" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="K59" s="13" t="s">
+      <c r="K59" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L59" s="1" t="s">
@@ -6907,22 +7263,22 @@
       <c r="I60" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="J60" s="13" t="s">
+      <c r="J60" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="K60" s="13" t="s">
+      <c r="K60" s="12" t="s">
         <v>291</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="2:12">
+    <row r="61" s="5" customFormat="1" customHeight="1" spans="2:12">
       <c r="B61" s="1"/>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="5" t="s">
         <v>318</v>
       </c>
       <c r="E61" s="1">
@@ -6931,7 +7287,7 @@
       <c r="F61" s="1">
         <v>2</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="5" t="s">
         <v>319</v>
       </c>
       <c r="H61" s="1" t="s">
@@ -6940,22 +7296,22 @@
       <c r="I61" s="1">
         <v>600</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="J61" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="K61" s="14" t="s">
+      <c r="K61" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="L61" s="2" t="s">
+      <c r="L61" s="5" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="2:12">
+    <row r="62" s="5" customFormat="1" customHeight="1" spans="2:12">
       <c r="B62" s="1"/>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="5" t="s">
         <v>325</v>
       </c>
       <c r="E62" s="1">
@@ -6964,7 +7320,7 @@
       <c r="F62" s="1">
         <v>2</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G62" s="5" t="s">
         <v>326</v>
       </c>
       <c r="H62" s="1" t="s">
@@ -6973,22 +7329,22 @@
       <c r="I62" s="1">
         <v>600</v>
       </c>
-      <c r="J62" s="14" t="s">
+      <c r="J62" s="13" t="s">
         <v>328</v>
       </c>
-      <c r="K62" s="14" t="s">
+      <c r="K62" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="L62" s="2" t="s">
+      <c r="L62" s="5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="2:12">
+    <row r="63" s="5" customFormat="1" customHeight="1" spans="2:12">
       <c r="B63" s="1"/>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="5" t="s">
         <v>331</v>
       </c>
       <c r="E63" s="1">
@@ -6997,7 +7353,7 @@
       <c r="F63" s="1">
         <v>2</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="5" t="s">
         <v>332</v>
       </c>
       <c r="H63" s="1" t="s">
@@ -7006,22 +7362,22 @@
       <c r="I63" s="1">
         <v>600</v>
       </c>
-      <c r="J63" s="14" t="s">
+      <c r="J63" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="K63" s="14" t="s">
+      <c r="K63" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="L63" s="2" t="s">
+      <c r="L63" s="5" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="2:12">
+    <row r="64" s="5" customFormat="1" customHeight="1" spans="2:12">
       <c r="B64" s="1"/>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="5" t="s">
         <v>337</v>
       </c>
       <c r="E64" s="1">
@@ -7030,7 +7386,7 @@
       <c r="F64" s="1">
         <v>2</v>
       </c>
-      <c r="G64" s="2" t="s">
+      <c r="G64" s="5" t="s">
         <v>338</v>
       </c>
       <c r="H64" s="1" t="s">
@@ -7039,22 +7395,22 @@
       <c r="I64" s="1">
         <v>600</v>
       </c>
-      <c r="J64" s="14" t="s">
+      <c r="J64" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="K64" s="14" t="s">
+      <c r="K64" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="L64" s="2" t="s">
+      <c r="L64" s="5" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="2:12">
+    <row r="65" s="5" customFormat="1" customHeight="1" spans="2:12">
       <c r="B65" s="1"/>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="5" t="s">
         <v>343</v>
       </c>
       <c r="E65" s="1">
@@ -7063,7 +7419,7 @@
       <c r="F65" s="1">
         <v>2</v>
       </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" s="5" t="s">
         <v>344</v>
       </c>
       <c r="H65" s="1" t="s">
@@ -7072,13 +7428,13 @@
       <c r="I65" s="1">
         <v>600</v>
       </c>
-      <c r="J65" s="14" t="s">
+      <c r="J65" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="K65" s="14" t="s">
+      <c r="K65" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="L65" s="2" t="s">
+      <c r="L65" s="5" t="s">
         <v>347</v>
       </c>
     </row>
@@ -7104,10 +7460,10 @@
       <c r="I66" s="1">
         <v>650</v>
       </c>
-      <c r="J66" s="14" t="s">
+      <c r="J66" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="K66" s="14" t="s">
+      <c r="K66" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L66" s="1" t="s">
@@ -7136,10 +7492,10 @@
       <c r="I67" s="1">
         <v>650</v>
       </c>
-      <c r="J67" s="14" t="s">
+      <c r="J67" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="K67" s="14" t="s">
+      <c r="K67" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L67" s="1" t="s">
@@ -7168,10 +7524,10 @@
       <c r="I68" s="1">
         <v>650</v>
       </c>
-      <c r="J68" s="14" t="s">
+      <c r="J68" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="K68" s="14" t="s">
+      <c r="K68" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L68" s="1" t="s">
@@ -7200,10 +7556,10 @@
       <c r="I69" s="1">
         <v>650</v>
       </c>
-      <c r="J69" s="14" t="s">
+      <c r="J69" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="K69" s="14" t="s">
+      <c r="K69" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L69" s="1" t="s">
@@ -7232,10 +7588,10 @@
       <c r="I70" s="1">
         <v>650</v>
       </c>
-      <c r="J70" s="14" t="s">
+      <c r="J70" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="K70" s="14" t="s">
+      <c r="K70" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L70" s="1" t="s">
@@ -7264,10 +7620,10 @@
       <c r="I71" s="1">
         <v>700</v>
       </c>
-      <c r="J71" s="14" t="s">
+      <c r="J71" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="14" t="s">
+      <c r="K71" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L71" s="1" t="s">
@@ -7296,10 +7652,10 @@
       <c r="I72" s="1">
         <v>700</v>
       </c>
-      <c r="J72" s="14" t="s">
+      <c r="J72" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="K72" s="14" t="s">
+      <c r="K72" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L72" s="1" t="s">
@@ -7328,10 +7684,10 @@
       <c r="I73" s="1">
         <v>700</v>
       </c>
-      <c r="J73" s="14" t="s">
+      <c r="J73" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="K73" s="14" t="s">
+      <c r="K73" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L73" s="1" t="s">
@@ -7360,10 +7716,10 @@
       <c r="I74" s="1">
         <v>700</v>
       </c>
-      <c r="J74" s="14" t="s">
+      <c r="J74" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="K74" s="14" t="s">
+      <c r="K74" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L74" s="1" t="s">
@@ -7392,10 +7748,10 @@
       <c r="I75" s="1">
         <v>700</v>
       </c>
-      <c r="J75" s="14" t="s">
+      <c r="J75" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="K75" s="14" t="s">
+      <c r="K75" s="13" t="s">
         <v>322</v>
       </c>
       <c r="L75" s="1" t="s">
@@ -7424,10 +7780,10 @@
       <c r="I76" s="1">
         <v>750</v>
       </c>
-      <c r="J76" s="14" t="s">
+      <c r="J76" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="K76" s="14" t="s">
+      <c r="K76" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L76" s="1" t="s">
@@ -7456,10 +7812,10 @@
       <c r="I77" s="1">
         <v>750</v>
       </c>
-      <c r="J77" s="14" t="s">
+      <c r="J77" s="13" t="s">
         <v>419</v>
       </c>
-      <c r="K77" s="14" t="s">
+      <c r="K77" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L77" s="1" t="s">
@@ -7488,10 +7844,10 @@
       <c r="I78" s="1">
         <v>750</v>
       </c>
-      <c r="J78" s="14" t="s">
+      <c r="J78" s="13" t="s">
         <v>425</v>
       </c>
-      <c r="K78" s="14" t="s">
+      <c r="K78" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L78" s="1" t="s">
@@ -7520,10 +7876,10 @@
       <c r="I79" s="1">
         <v>750</v>
       </c>
-      <c r="J79" s="14" t="s">
+      <c r="J79" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="K79" s="14" t="s">
+      <c r="K79" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L79" s="1" t="s">
@@ -7552,10 +7908,10 @@
       <c r="I80" s="1">
         <v>750</v>
       </c>
-      <c r="J80" s="14" t="s">
+      <c r="J80" s="13" t="s">
         <v>437</v>
       </c>
-      <c r="K80" s="14" t="s">
+      <c r="K80" s="13" t="s">
         <v>413</v>
       </c>
       <c r="L80" s="1" t="s">
@@ -7584,10 +7940,10 @@
       <c r="I81" s="1">
         <v>800</v>
       </c>
-      <c r="J81" s="14" t="s">
+      <c r="J81" s="13" t="s">
         <v>443</v>
       </c>
-      <c r="K81" s="14" t="s">
+      <c r="K81" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L81" s="1" t="s">
@@ -7616,10 +7972,10 @@
       <c r="I82" s="1">
         <v>800</v>
       </c>
-      <c r="J82" s="14" t="s">
+      <c r="J82" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="K82" s="14" t="s">
+      <c r="K82" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L82" s="1" t="s">
@@ -7648,10 +8004,10 @@
       <c r="I83" s="1">
         <v>800</v>
       </c>
-      <c r="J83" s="14" t="s">
+      <c r="J83" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="K83" s="14" t="s">
+      <c r="K83" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L83" s="1" t="s">
@@ -7680,10 +8036,10 @@
       <c r="I84" s="1">
         <v>800</v>
       </c>
-      <c r="J84" s="14" t="s">
+      <c r="J84" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="K84" s="14" t="s">
+      <c r="K84" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L84" s="1" t="s">
@@ -7712,10 +8068,10 @@
       <c r="I85" s="1">
         <v>800</v>
       </c>
-      <c r="J85" s="14" t="s">
+      <c r="J85" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="K85" s="14" t="s">
+      <c r="K85" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L85" s="1" t="s">
@@ -7744,10 +8100,10 @@
       <c r="I86" s="1">
         <v>850</v>
       </c>
-      <c r="J86" s="14" t="s">
+      <c r="J86" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="K86" s="14" t="s">
+      <c r="K86" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L86" s="1" t="s">
@@ -7776,10 +8132,10 @@
       <c r="I87" s="1">
         <v>850</v>
       </c>
-      <c r="J87" s="14" t="s">
+      <c r="J87" s="13" t="s">
         <v>480</v>
       </c>
-      <c r="K87" s="14" t="s">
+      <c r="K87" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L87" s="1" t="s">
@@ -7808,10 +8164,10 @@
       <c r="I88" s="1">
         <v>850</v>
       </c>
-      <c r="J88" s="14" t="s">
+      <c r="J88" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="K88" s="14" t="s">
+      <c r="K88" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L88" s="1" t="s">
@@ -7840,10 +8196,10 @@
       <c r="I89" s="1">
         <v>850</v>
       </c>
-      <c r="J89" s="14" t="s">
+      <c r="J89" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="K89" s="14" t="s">
+      <c r="K89" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L89" s="1" t="s">
@@ -7872,10 +8228,10 @@
       <c r="I90" s="1">
         <v>850</v>
       </c>
-      <c r="J90" s="14" t="s">
+      <c r="J90" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="K90" s="14" t="s">
+      <c r="K90" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L90" s="1" t="s">
@@ -7904,10 +8260,10 @@
       <c r="I91" s="1">
         <v>900</v>
       </c>
-      <c r="J91" s="14" t="s">
+      <c r="J91" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="K91" s="14" t="s">
+      <c r="K91" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L91" s="1" t="s">
@@ -7936,10 +8292,10 @@
       <c r="I92" s="1">
         <v>900</v>
       </c>
-      <c r="J92" s="14" t="s">
+      <c r="J92" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="K92" s="14" t="s">
+      <c r="K92" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L92" s="1" t="s">
@@ -7968,10 +8324,10 @@
       <c r="I93" s="1">
         <v>900</v>
       </c>
-      <c r="J93" s="14" t="s">
+      <c r="J93" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="K93" s="14" t="s">
+      <c r="K93" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L93" s="1" t="s">
@@ -8000,10 +8356,10 @@
       <c r="I94" s="1">
         <v>900</v>
       </c>
-      <c r="J94" s="14" t="s">
+      <c r="J94" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="K94" s="14" t="s">
+      <c r="K94" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L94" s="1" t="s">
@@ -8032,10 +8388,10 @@
       <c r="I95" s="1">
         <v>900</v>
       </c>
-      <c r="J95" s="14" t="s">
+      <c r="J95" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="K95" s="14" t="s">
+      <c r="K95" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L95" s="1" t="s">
@@ -8046,7 +8402,7 @@
       <c r="C96" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="5" t="s">
         <v>531</v>
       </c>
       <c r="E96" s="1">
@@ -8064,10 +8420,10 @@
       <c r="I96" s="1">
         <v>950</v>
       </c>
-      <c r="J96" s="14" t="s">
+      <c r="J96" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="K96" s="14" t="s">
+      <c r="K96" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L96" s="1" t="s">
@@ -8078,7 +8434,7 @@
       <c r="C97" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="5" t="s">
         <v>537</v>
       </c>
       <c r="E97" s="1">
@@ -8096,10 +8452,10 @@
       <c r="I97" s="1">
         <v>950</v>
       </c>
-      <c r="J97" s="14" t="s">
+      <c r="J97" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="K97" s="14" t="s">
+      <c r="K97" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L97" s="1" t="s">
@@ -8110,7 +8466,7 @@
       <c r="C98" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="5" t="s">
         <v>543</v>
       </c>
       <c r="E98" s="1">
@@ -8128,10 +8484,10 @@
       <c r="I98" s="1">
         <v>950</v>
       </c>
-      <c r="J98" s="14" t="s">
+      <c r="J98" s="13" t="s">
         <v>546</v>
       </c>
-      <c r="K98" s="14" t="s">
+      <c r="K98" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L98" s="1" t="s">
@@ -8142,7 +8498,7 @@
       <c r="C99" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="5" t="s">
         <v>549</v>
       </c>
       <c r="E99" s="1">
@@ -8160,10 +8516,10 @@
       <c r="I99" s="1">
         <v>950</v>
       </c>
-      <c r="J99" s="14" t="s">
+      <c r="J99" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="K99" s="14" t="s">
+      <c r="K99" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L99" s="1" t="s">
@@ -8174,7 +8530,7 @@
       <c r="C100" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="D100" s="2" t="s">
+      <c r="D100" s="5" t="s">
         <v>555</v>
       </c>
       <c r="E100" s="1">
@@ -8192,10 +8548,10 @@
       <c r="I100" s="1">
         <v>950</v>
       </c>
-      <c r="J100" s="14" t="s">
+      <c r="J100" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="K100" s="14" t="s">
+      <c r="K100" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L100" s="1" t="s">
@@ -8224,10 +8580,10 @@
       <c r="I101" s="1">
         <v>1000</v>
       </c>
-      <c r="J101" s="14" t="s">
+      <c r="J101" s="13" t="s">
         <v>564</v>
       </c>
-      <c r="K101" s="14" t="s">
+      <c r="K101" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L101" s="1" t="s">
@@ -8256,10 +8612,10 @@
       <c r="I102" s="1">
         <v>1000</v>
       </c>
-      <c r="J102" s="14" t="s">
+      <c r="J102" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="K102" s="14" t="s">
+      <c r="K102" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L102" s="1" t="s">
@@ -8288,10 +8644,10 @@
       <c r="I103" s="1">
         <v>1000</v>
       </c>
-      <c r="J103" s="14" t="s">
+      <c r="J103" s="13" t="s">
         <v>576</v>
       </c>
-      <c r="K103" s="14" t="s">
+      <c r="K103" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L103" s="1" t="s">
@@ -8320,10 +8676,10 @@
       <c r="I104" s="1">
         <v>1000</v>
       </c>
-      <c r="J104" s="14" t="s">
+      <c r="J104" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="K104" s="14" t="s">
+      <c r="K104" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L104" s="1" t="s">
@@ -8352,10 +8708,10 @@
       <c r="I105" s="1">
         <v>1000</v>
       </c>
-      <c r="J105" s="14" t="s">
+      <c r="J105" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="K105" s="14" t="s">
+      <c r="K105" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L105" s="1" t="s">
@@ -8384,10 +8740,10 @@
       <c r="I106" s="1">
         <v>1050</v>
       </c>
-      <c r="J106" s="14" t="s">
+      <c r="J106" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="K106" s="14" t="s">
+      <c r="K106" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L106" s="1" t="s">
@@ -8416,10 +8772,10 @@
       <c r="I107" s="1">
         <v>1050</v>
       </c>
-      <c r="J107" s="14" t="s">
+      <c r="J107" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="K107" s="14" t="s">
+      <c r="K107" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L107" s="1" t="s">
@@ -8448,10 +8804,10 @@
       <c r="I108" s="1">
         <v>1050</v>
       </c>
-      <c r="J108" s="14" t="s">
+      <c r="J108" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="K108" s="14" t="s">
+      <c r="K108" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L108" s="1" t="s">
@@ -8480,10 +8836,10 @@
       <c r="I109" s="1">
         <v>1050</v>
       </c>
-      <c r="J109" s="14" t="s">
+      <c r="J109" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="K109" s="14" t="s">
+      <c r="K109" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L109" s="1" t="s">
@@ -8512,10 +8868,10 @@
       <c r="I110" s="1">
         <v>1050</v>
       </c>
-      <c r="J110" s="14" t="s">
+      <c r="J110" s="13" t="s">
         <v>618</v>
       </c>
-      <c r="K110" s="14" t="s">
+      <c r="K110" s="13" t="s">
         <v>444</v>
       </c>
       <c r="L110" s="1" t="s">
@@ -8544,10 +8900,10 @@
       <c r="I111" s="1">
         <v>0</v>
       </c>
-      <c r="J111" s="14" t="s">
+      <c r="J111" s="13" t="s">
         <v>624</v>
       </c>
-      <c r="K111" s="14" t="s">
+      <c r="K111" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L111" s="1" t="s">
@@ -8576,10 +8932,10 @@
       <c r="I112" s="1">
         <v>0</v>
       </c>
-      <c r="J112" s="14" t="s">
+      <c r="J112" s="13" t="s">
         <v>631</v>
       </c>
-      <c r="K112" s="14" t="s">
+      <c r="K112" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L112" s="1" t="s">
@@ -8608,10 +8964,10 @@
       <c r="I113" s="1">
         <v>0</v>
       </c>
-      <c r="J113" s="14" t="s">
+      <c r="J113" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="K113" s="14" t="s">
+      <c r="K113" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L113" s="1" t="s">
@@ -8640,10 +8996,10 @@
       <c r="I114" s="1">
         <v>0</v>
       </c>
-      <c r="J114" s="14" t="s">
+      <c r="J114" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="K114" s="14" t="s">
+      <c r="K114" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L114" s="1" t="s">
@@ -8672,10 +9028,10 @@
       <c r="I115" s="1">
         <v>0</v>
       </c>
-      <c r="J115" s="14" t="s">
+      <c r="J115" s="13" t="s">
         <v>649</v>
       </c>
-      <c r="K115" s="14" t="s">
+      <c r="K115" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L115" s="1" t="s">
@@ -8704,10 +9060,10 @@
       <c r="I116" s="1">
         <v>0</v>
       </c>
-      <c r="J116" s="14" t="s">
+      <c r="J116" s="13" t="s">
         <v>655</v>
       </c>
-      <c r="K116" s="14" t="s">
+      <c r="K116" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L116" s="1" t="s">
@@ -8736,10 +9092,10 @@
       <c r="I117" s="1">
         <v>0</v>
       </c>
-      <c r="J117" s="14" t="s">
+      <c r="J117" s="13" t="s">
         <v>661</v>
       </c>
-      <c r="K117" s="14" t="s">
+      <c r="K117" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L117" s="1" t="s">
@@ -8768,10 +9124,10 @@
       <c r="I118" s="1">
         <v>0</v>
       </c>
-      <c r="J118" s="14" t="s">
+      <c r="J118" s="13" t="s">
         <v>667</v>
       </c>
-      <c r="K118" s="14" t="s">
+      <c r="K118" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L118" s="1" t="s">
@@ -8800,10 +9156,10 @@
       <c r="I119" s="1">
         <v>0</v>
       </c>
-      <c r="J119" s="14" t="s">
+      <c r="J119" s="13" t="s">
         <v>673</v>
       </c>
-      <c r="K119" s="14" t="s">
+      <c r="K119" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L119" s="1" t="s">
@@ -8832,10 +9188,10 @@
       <c r="I120" s="1">
         <v>0</v>
       </c>
-      <c r="J120" s="14" t="s">
+      <c r="J120" s="13" t="s">
         <v>679</v>
       </c>
-      <c r="K120" s="14" t="s">
+      <c r="K120" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L120" s="1" t="s">
@@ -8864,10 +9220,10 @@
       <c r="I121" s="1">
         <v>0</v>
       </c>
-      <c r="J121" s="14" t="s">
+      <c r="J121" s="13" t="s">
         <v>685</v>
       </c>
-      <c r="K121" s="14" t="s">
+      <c r="K121" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L121" s="1" t="s">
@@ -8896,10 +9252,10 @@
       <c r="I122" s="1">
         <v>0</v>
       </c>
-      <c r="J122" s="14" t="s">
+      <c r="J122" s="13" t="s">
         <v>691</v>
       </c>
-      <c r="K122" s="14" t="s">
+      <c r="K122" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L122" s="1" t="s">
@@ -8928,10 +9284,10 @@
       <c r="I123" s="1">
         <v>0</v>
       </c>
-      <c r="J123" s="14" t="s">
+      <c r="J123" s="13" t="s">
         <v>697</v>
       </c>
-      <c r="K123" s="14" t="s">
+      <c r="K123" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L123" s="1" t="s">
@@ -8960,10 +9316,10 @@
       <c r="I124" s="1">
         <v>0</v>
       </c>
-      <c r="J124" s="14" t="s">
+      <c r="J124" s="13" t="s">
         <v>703</v>
       </c>
-      <c r="K124" s="14" t="s">
+      <c r="K124" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L124" s="1" t="s">
@@ -8992,10 +9348,10 @@
       <c r="I125" s="1">
         <v>0</v>
       </c>
-      <c r="J125" s="14" t="s">
+      <c r="J125" s="13" t="s">
         <v>709</v>
       </c>
-      <c r="K125" s="14" t="s">
+      <c r="K125" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L125" s="1" t="s">
@@ -9024,10 +9380,10 @@
       <c r="I126" s="1">
         <v>0</v>
       </c>
-      <c r="J126" s="14" t="s">
+      <c r="J126" s="13" t="s">
         <v>715</v>
       </c>
-      <c r="K126" s="14" t="s">
+      <c r="K126" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L126" s="1" t="s">
@@ -9056,10 +9412,10 @@
       <c r="I127" s="1">
         <v>0</v>
       </c>
-      <c r="J127" s="14" t="s">
+      <c r="J127" s="13" t="s">
         <v>721</v>
       </c>
-      <c r="K127" s="14" t="s">
+      <c r="K127" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L127" s="1" t="s">
@@ -9088,10 +9444,10 @@
       <c r="I128" s="1">
         <v>0</v>
       </c>
-      <c r="J128" s="14" t="s">
+      <c r="J128" s="13" t="s">
         <v>727</v>
       </c>
-      <c r="K128" s="14" t="s">
+      <c r="K128" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L128" s="1" t="s">
@@ -9120,10 +9476,10 @@
       <c r="I129" s="1">
         <v>0</v>
       </c>
-      <c r="J129" s="14" t="s">
+      <c r="J129" s="13" t="s">
         <v>733</v>
       </c>
-      <c r="K129" s="14" t="s">
+      <c r="K129" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L129" s="1" t="s">
@@ -9152,10 +9508,10 @@
       <c r="I130" s="1">
         <v>0</v>
       </c>
-      <c r="J130" s="14" t="s">
+      <c r="J130" s="13" t="s">
         <v>739</v>
       </c>
-      <c r="K130" s="14" t="s">
+      <c r="K130" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L130" s="1" t="s">
@@ -9166,7 +9522,7 @@
       <c r="C131" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="D131" s="2" t="s">
+      <c r="D131" s="5" t="s">
         <v>742</v>
       </c>
       <c r="E131" s="1">
@@ -9184,10 +9540,10 @@
       <c r="I131" s="1">
         <v>0</v>
       </c>
-      <c r="J131" s="14" t="s">
+      <c r="J131" s="13" t="s">
         <v>745</v>
       </c>
-      <c r="K131" s="14" t="s">
+      <c r="K131" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L131" s="1" t="s">
@@ -9198,7 +9554,7 @@
       <c r="C132" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D132" s="5" t="s">
         <v>748</v>
       </c>
       <c r="E132" s="1">
@@ -9216,10 +9572,10 @@
       <c r="I132" s="1">
         <v>0</v>
       </c>
-      <c r="J132" s="14" t="s">
+      <c r="J132" s="13" t="s">
         <v>751</v>
       </c>
-      <c r="K132" s="14" t="s">
+      <c r="K132" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L132" s="1" t="s">
@@ -9230,7 +9586,7 @@
       <c r="C133" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="D133" s="5" t="s">
         <v>754</v>
       </c>
       <c r="E133" s="1">
@@ -9248,10 +9604,10 @@
       <c r="I133" s="1">
         <v>0</v>
       </c>
-      <c r="J133" s="14" t="s">
+      <c r="J133" s="13" t="s">
         <v>757</v>
       </c>
-      <c r="K133" s="14" t="s">
+      <c r="K133" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L133" s="1" t="s">
@@ -9262,7 +9618,7 @@
       <c r="C134" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="D134" s="5" t="s">
         <v>760</v>
       </c>
       <c r="E134" s="1">
@@ -9280,10 +9636,10 @@
       <c r="I134" s="1">
         <v>0</v>
       </c>
-      <c r="J134" s="14" t="s">
+      <c r="J134" s="13" t="s">
         <v>763</v>
       </c>
-      <c r="K134" s="14" t="s">
+      <c r="K134" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L134" s="1" t="s">
@@ -9294,7 +9650,7 @@
       <c r="C135" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="D135" s="2" t="s">
+      <c r="D135" s="5" t="s">
         <v>766</v>
       </c>
       <c r="E135" s="1">
@@ -9312,10 +9668,10 @@
       <c r="I135" s="1">
         <v>0</v>
       </c>
-      <c r="J135" s="14" t="s">
+      <c r="J135" s="13" t="s">
         <v>769</v>
       </c>
-      <c r="K135" s="14" t="s">
+      <c r="K135" s="13" t="s">
         <v>625</v>
       </c>
       <c r="L135" s="1" t="s">
@@ -9344,10 +9700,10 @@
       <c r="I136" s="1">
         <v>0</v>
       </c>
-      <c r="J136" s="14" t="s">
+      <c r="J136" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="K136" s="14" t="s">
+      <c r="K136" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L136" s="1" t="s">
@@ -9376,10 +9732,10 @@
       <c r="I137" s="1">
         <v>0</v>
       </c>
-      <c r="J137" s="14" t="s">
+      <c r="J137" s="13" t="s">
         <v>782</v>
       </c>
-      <c r="K137" s="14" t="s">
+      <c r="K137" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L137" s="1" t="s">
@@ -9408,10 +9764,10 @@
       <c r="I138" s="1">
         <v>0</v>
       </c>
-      <c r="J138" s="14" t="s">
+      <c r="J138" s="13" t="s">
         <v>788</v>
       </c>
-      <c r="K138" s="14" t="s">
+      <c r="K138" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L138" s="1" t="s">
@@ -9440,10 +9796,10 @@
       <c r="I139" s="1">
         <v>0</v>
       </c>
-      <c r="J139" s="14" t="s">
+      <c r="J139" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="K139" s="14" t="s">
+      <c r="K139" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L139" s="1" t="s">
@@ -9472,10 +9828,10 @@
       <c r="I140" s="1">
         <v>0</v>
       </c>
-      <c r="J140" s="14" t="s">
+      <c r="J140" s="13" t="s">
         <v>800</v>
       </c>
-      <c r="K140" s="14" t="s">
+      <c r="K140" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L140" s="1" t="s">
@@ -9504,10 +9860,10 @@
       <c r="I141" s="1">
         <v>0</v>
       </c>
-      <c r="J141" s="14" t="s">
+      <c r="J141" s="13" t="s">
         <v>806</v>
       </c>
-      <c r="K141" s="14" t="s">
+      <c r="K141" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L141" s="1" t="s">
@@ -9536,10 +9892,10 @@
       <c r="I142" s="1">
         <v>0</v>
       </c>
-      <c r="J142" s="14" t="s">
+      <c r="J142" s="13" t="s">
         <v>812</v>
       </c>
-      <c r="K142" s="14" t="s">
+      <c r="K142" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L142" s="1" t="s">
@@ -9568,10 +9924,10 @@
       <c r="I143" s="1">
         <v>0</v>
       </c>
-      <c r="J143" s="14" t="s">
+      <c r="J143" s="13" t="s">
         <v>818</v>
       </c>
-      <c r="K143" s="14" t="s">
+      <c r="K143" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L143" s="1" t="s">
@@ -9600,10 +9956,10 @@
       <c r="I144" s="1">
         <v>0</v>
       </c>
-      <c r="J144" s="14" t="s">
+      <c r="J144" s="13" t="s">
         <v>824</v>
       </c>
-      <c r="K144" s="14" t="s">
+      <c r="K144" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L144" s="1" t="s">
@@ -9632,45 +9988,45 @@
       <c r="I145" s="1">
         <v>0</v>
       </c>
-      <c r="J145" s="14" t="s">
+      <c r="J145" s="13" t="s">
         <v>830</v>
       </c>
-      <c r="K145" s="14" t="s">
+      <c r="K145" s="13" t="s">
         <v>776</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="146" s="3" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C146" s="3" t="s">
+    <row r="146" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C146" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D146" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="E146" s="3">
+      <c r="E146" s="2">
         <v>5</v>
       </c>
-      <c r="F146" s="3">
+      <c r="F146" s="2">
         <v>5</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" s="2" t="s">
         <v>834</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="I146" s="3">
-        <v>0</v>
-      </c>
-      <c r="J146" s="15" t="s">
+      <c r="I146" s="2">
+        <v>0</v>
+      </c>
+      <c r="J146" s="14" t="s">
         <v>836</v>
       </c>
-      <c r="K146" s="15" t="s">
+      <c r="K146" s="14" t="s">
         <v>776</v>
       </c>
-      <c r="L146" s="15" t="s">
+      <c r="L146" s="14" t="s">
         <v>837</v>
       </c>
     </row>
@@ -9696,13 +10052,13 @@
       <c r="I147" s="1">
         <v>0</v>
       </c>
-      <c r="J147" s="14" t="s">
+      <c r="J147" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K147" s="14" t="s">
+      <c r="K147" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L147" s="13" t="s">
+      <c r="L147" s="12" t="s">
         <v>842</v>
       </c>
     </row>
@@ -9728,13 +10084,13 @@
       <c r="I148" s="1">
         <v>0</v>
       </c>
-      <c r="J148" s="14" t="s">
+      <c r="J148" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K148" s="14" t="s">
+      <c r="K148" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L148" s="13" t="s">
+      <c r="L148" s="12" t="s">
         <v>847</v>
       </c>
     </row>
@@ -9760,13 +10116,13 @@
       <c r="I149" s="1">
         <v>0</v>
       </c>
-      <c r="J149" s="14" t="s">
+      <c r="J149" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K149" s="14" t="s">
+      <c r="K149" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L149" s="13" t="s">
+      <c r="L149" s="12" t="s">
         <v>852</v>
       </c>
     </row>
@@ -9792,13 +10148,13 @@
       <c r="I150" s="1">
         <v>0</v>
       </c>
-      <c r="J150" s="14" t="s">
+      <c r="J150" s="13" t="s">
         <v>836</v>
       </c>
-      <c r="K150" s="14" t="s">
+      <c r="K150" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L150" s="13" t="s">
+      <c r="L150" s="12" t="s">
         <v>857</v>
       </c>
     </row>
@@ -9824,13 +10180,13 @@
       <c r="I151" s="1">
         <v>0</v>
       </c>
-      <c r="J151" s="14" t="s">
+      <c r="J151" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K151" s="14" t="s">
+      <c r="K151" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L151" s="13" t="s">
+      <c r="L151" s="12" t="s">
         <v>863</v>
       </c>
     </row>
@@ -9856,13 +10212,13 @@
       <c r="I152" s="1">
         <v>0</v>
       </c>
-      <c r="J152" s="14" t="s">
+      <c r="J152" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K152" s="14" t="s">
+      <c r="K152" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L152" s="13" t="s">
+      <c r="L152" s="12" t="s">
         <v>868</v>
       </c>
     </row>
@@ -9888,13 +10244,13 @@
       <c r="I153" s="1">
         <v>0</v>
       </c>
-      <c r="J153" s="14" t="s">
+      <c r="J153" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K153" s="14" t="s">
+      <c r="K153" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L153" s="13" t="s">
+      <c r="L153" s="12" t="s">
         <v>873</v>
       </c>
     </row>
@@ -9920,13 +10276,13 @@
       <c r="I154" s="1">
         <v>0</v>
       </c>
-      <c r="J154" s="14" t="s">
+      <c r="J154" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K154" s="14" t="s">
+      <c r="K154" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L154" s="13" t="s">
+      <c r="L154" s="12" t="s">
         <v>878</v>
       </c>
     </row>
@@ -9952,13 +10308,13 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="14" t="s">
+      <c r="J155" s="13" t="s">
         <v>862</v>
       </c>
-      <c r="K155" s="14" t="s">
+      <c r="K155" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L155" s="13" t="s">
+      <c r="L155" s="12" t="s">
         <v>883</v>
       </c>
     </row>
@@ -9984,13 +10340,13 @@
       <c r="I156" s="1">
         <v>0</v>
       </c>
-      <c r="J156" s="14" t="s">
+      <c r="J156" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K156" s="14" t="s">
+      <c r="K156" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L156" s="13" t="s">
+      <c r="L156" s="12" t="s">
         <v>889</v>
       </c>
     </row>
@@ -10016,13 +10372,13 @@
       <c r="I157" s="1">
         <v>0</v>
       </c>
-      <c r="J157" s="14" t="s">
+      <c r="J157" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K157" s="14" t="s">
+      <c r="K157" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L157" s="13" t="s">
+      <c r="L157" s="12" t="s">
         <v>894</v>
       </c>
     </row>
@@ -10048,13 +10404,13 @@
       <c r="I158" s="1">
         <v>0</v>
       </c>
-      <c r="J158" s="14" t="s">
+      <c r="J158" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K158" s="14" t="s">
+      <c r="K158" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L158" s="13" t="s">
+      <c r="L158" s="12" t="s">
         <v>899</v>
       </c>
     </row>
@@ -10080,13 +10436,13 @@
       <c r="I159" s="1">
         <v>0</v>
       </c>
-      <c r="J159" s="14" t="s">
+      <c r="J159" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K159" s="14" t="s">
+      <c r="K159" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L159" s="13" t="s">
+      <c r="L159" s="12" t="s">
         <v>904</v>
       </c>
     </row>
@@ -10112,13 +10468,13 @@
       <c r="I160" s="1">
         <v>0</v>
       </c>
-      <c r="J160" s="14" t="s">
+      <c r="J160" s="13" t="s">
         <v>888</v>
       </c>
-      <c r="K160" s="14" t="s">
+      <c r="K160" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L160" s="13" t="s">
+      <c r="L160" s="12" t="s">
         <v>909</v>
       </c>
     </row>
@@ -10144,13 +10500,13 @@
       <c r="I161" s="1">
         <v>0</v>
       </c>
-      <c r="J161" s="14" t="s">
+      <c r="J161" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K161" s="14" t="s">
+      <c r="K161" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L161" s="13" t="s">
+      <c r="L161" s="12" t="s">
         <v>915</v>
       </c>
     </row>
@@ -10176,13 +10532,13 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="J162" s="14" t="s">
+      <c r="J162" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K162" s="14" t="s">
+      <c r="K162" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L162" s="13" t="s">
+      <c r="L162" s="12" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10208,13 +10564,13 @@
       <c r="I163" s="1">
         <v>0</v>
       </c>
-      <c r="J163" s="14" t="s">
+      <c r="J163" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K163" s="14" t="s">
+      <c r="K163" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L163" s="13" t="s">
+      <c r="L163" s="12" t="s">
         <v>925</v>
       </c>
     </row>
@@ -10240,13 +10596,13 @@
       <c r="I164" s="1">
         <v>0</v>
       </c>
-      <c r="J164" s="14" t="s">
+      <c r="J164" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K164" s="14" t="s">
+      <c r="K164" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L164" s="13" t="s">
+      <c r="L164" s="12" t="s">
         <v>930</v>
       </c>
     </row>
@@ -10272,13 +10628,13 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="J165" s="14" t="s">
+      <c r="J165" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="K165" s="14" t="s">
+      <c r="K165" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L165" s="13" t="s">
+      <c r="L165" s="12" t="s">
         <v>935</v>
       </c>
     </row>
@@ -10286,7 +10642,7 @@
       <c r="C166" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="D166" s="2" t="s">
+      <c r="D166" s="5" t="s">
         <v>937</v>
       </c>
       <c r="E166" s="1">
@@ -10304,13 +10660,13 @@
       <c r="I166" s="1">
         <v>0</v>
       </c>
-      <c r="J166" s="14" t="s">
+      <c r="J166" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K166" s="14" t="s">
+      <c r="K166" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L166" s="13" t="s">
+      <c r="L166" s="12" t="s">
         <v>941</v>
       </c>
     </row>
@@ -10318,7 +10674,7 @@
       <c r="C167" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="D167" s="2" t="s">
+      <c r="D167" s="5" t="s">
         <v>943</v>
       </c>
       <c r="E167" s="1">
@@ -10336,13 +10692,13 @@
       <c r="I167" s="1">
         <v>0</v>
       </c>
-      <c r="J167" s="14" t="s">
+      <c r="J167" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K167" s="14" t="s">
+      <c r="K167" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L167" s="13" t="s">
+      <c r="L167" s="12" t="s">
         <v>946</v>
       </c>
     </row>
@@ -10350,7 +10706,7 @@
       <c r="C168" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="D168" s="2" t="s">
+      <c r="D168" s="5" t="s">
         <v>948</v>
       </c>
       <c r="E168" s="1">
@@ -10368,13 +10724,13 @@
       <c r="I168" s="1">
         <v>0</v>
       </c>
-      <c r="J168" s="14" t="s">
+      <c r="J168" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K168" s="14" t="s">
+      <c r="K168" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L168" s="13" t="s">
+      <c r="L168" s="12" t="s">
         <v>951</v>
       </c>
     </row>
@@ -10382,7 +10738,7 @@
       <c r="C169" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="D169" s="5" t="s">
         <v>953</v>
       </c>
       <c r="E169" s="1">
@@ -10400,13 +10756,13 @@
       <c r="I169" s="1">
         <v>0</v>
       </c>
-      <c r="J169" s="14" t="s">
+      <c r="J169" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K169" s="14" t="s">
+      <c r="K169" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L169" s="13" t="s">
+      <c r="L169" s="12" t="s">
         <v>956</v>
       </c>
     </row>
@@ -10414,7 +10770,7 @@
       <c r="C170" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="D170" s="2" t="s">
+      <c r="D170" s="5" t="s">
         <v>958</v>
       </c>
       <c r="E170" s="1">
@@ -10432,13 +10788,13 @@
       <c r="I170" s="1">
         <v>0</v>
       </c>
-      <c r="J170" s="14" t="s">
+      <c r="J170" s="13" t="s">
         <v>940</v>
       </c>
-      <c r="K170" s="14" t="s">
+      <c r="K170" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L170" s="13" t="s">
+      <c r="L170" s="12" t="s">
         <v>961</v>
       </c>
     </row>
@@ -10464,13 +10820,13 @@
       <c r="I171" s="1">
         <v>0</v>
       </c>
-      <c r="J171" s="14" t="s">
+      <c r="J171" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K171" s="14" t="s">
+      <c r="K171" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L171" s="13" t="s">
+      <c r="L171" s="12" t="s">
         <v>967</v>
       </c>
     </row>
@@ -10496,13 +10852,13 @@
       <c r="I172" s="1">
         <v>0</v>
       </c>
-      <c r="J172" s="14" t="s">
+      <c r="J172" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K172" s="14" t="s">
+      <c r="K172" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L172" s="13" t="s">
+      <c r="L172" s="12" t="s">
         <v>972</v>
       </c>
     </row>
@@ -10528,13 +10884,13 @@
       <c r="I173" s="1">
         <v>0</v>
       </c>
-      <c r="J173" s="14" t="s">
+      <c r="J173" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K173" s="14" t="s">
+      <c r="K173" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L173" s="13" t="s">
+      <c r="L173" s="12" t="s">
         <v>977</v>
       </c>
     </row>
@@ -10560,13 +10916,13 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
-      <c r="J174" s="14" t="s">
+      <c r="J174" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K174" s="14" t="s">
+      <c r="K174" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L174" s="13" t="s">
+      <c r="L174" s="12" t="s">
         <v>982</v>
       </c>
     </row>
@@ -10592,13 +10948,13 @@
       <c r="I175" s="1">
         <v>0</v>
       </c>
-      <c r="J175" s="14" t="s">
+      <c r="J175" s="13" t="s">
         <v>966</v>
       </c>
-      <c r="K175" s="14" t="s">
+      <c r="K175" s="13" t="s">
         <v>776</v>
       </c>
-      <c r="L175" s="13" t="s">
+      <c r="L175" s="12" t="s">
         <v>987</v>
       </c>
     </row>
@@ -10624,13 +10980,13 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
-      <c r="J176" s="14" t="s">
+      <c r="J176" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K176" s="14" t="s">
+      <c r="K176" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L176" s="13" t="s">
+      <c r="L176" s="12" t="s">
         <v>994</v>
       </c>
     </row>
@@ -10656,13 +11012,13 @@
       <c r="I177" s="1">
         <v>0</v>
       </c>
-      <c r="J177" s="14" t="s">
+      <c r="J177" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K177" s="14" t="s">
+      <c r="K177" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L177" s="13" t="s">
+      <c r="L177" s="12" t="s">
         <v>999</v>
       </c>
     </row>
@@ -10688,13 +11044,13 @@
       <c r="I178" s="1">
         <v>0</v>
       </c>
-      <c r="J178" s="14" t="s">
+      <c r="J178" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K178" s="14" t="s">
+      <c r="K178" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L178" s="13" t="s">
+      <c r="L178" s="12" t="s">
         <v>1004</v>
       </c>
     </row>
@@ -10720,13 +11076,13 @@
       <c r="I179" s="1">
         <v>0</v>
       </c>
-      <c r="J179" s="14" t="s">
+      <c r="J179" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K179" s="14" t="s">
+      <c r="K179" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L179" s="13" t="s">
+      <c r="L179" s="12" t="s">
         <v>1009</v>
       </c>
     </row>
@@ -10752,45 +11108,45 @@
       <c r="I180" s="1">
         <v>0</v>
       </c>
-      <c r="J180" s="14" t="s">
+      <c r="J180" s="13" t="s">
         <v>992</v>
       </c>
-      <c r="K180" s="14" t="s">
+      <c r="K180" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="L180" s="13" t="s">
+      <c r="L180" s="12" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="181" s="3" customFormat="1" customHeight="1" spans="3:12">
+    <row r="181" s="2" customFormat="1" customHeight="1" spans="3:12">
       <c r="C181" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="D181" s="2" t="s">
         <v>1016</v>
       </c>
-      <c r="E181" s="3">
+      <c r="E181" s="2">
         <v>5</v>
       </c>
-      <c r="F181" s="3">
+      <c r="F181" s="2">
         <v>5</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="2" t="s">
         <v>1017</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="I181" s="3">
-        <v>0</v>
-      </c>
-      <c r="J181" s="15" t="s">
+      <c r="I181" s="2">
+        <v>0</v>
+      </c>
+      <c r="J181" s="14" t="s">
         <v>1019</v>
       </c>
-      <c r="K181" s="15" t="s">
+      <c r="K181" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="L181" s="13" t="s">
+      <c r="L181" s="12" t="s">
         <v>1021</v>
       </c>
     </row>
@@ -10816,13 +11172,13 @@
       <c r="I182" s="1">
         <v>0</v>
       </c>
-      <c r="J182" s="14" t="s">
+      <c r="J182" s="13" t="s">
         <v>1026</v>
       </c>
-      <c r="K182" s="14" t="s">
+      <c r="K182" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L182" s="13" t="s">
+      <c r="L182" s="12" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -10848,13 +11204,13 @@
       <c r="I183" s="1">
         <v>0</v>
       </c>
-      <c r="J183" s="14" t="s">
+      <c r="J183" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="K183" s="14" t="s">
+      <c r="K183" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L183" s="13" t="s">
+      <c r="L183" s="12" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10880,13 +11236,13 @@
       <c r="I184" s="1">
         <v>0</v>
       </c>
-      <c r="J184" s="14" t="s">
+      <c r="J184" s="13" t="s">
         <v>1038</v>
       </c>
-      <c r="K184" s="14" t="s">
+      <c r="K184" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L184" s="13" t="s">
+      <c r="L184" s="12" t="s">
         <v>1039</v>
       </c>
     </row>
@@ -10912,13 +11268,13 @@
       <c r="I185" s="1">
         <v>0</v>
       </c>
-      <c r="J185" s="14" t="s">
+      <c r="J185" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="K185" s="14" t="s">
+      <c r="K185" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L185" s="13" t="s">
+      <c r="L185" s="12" t="s">
         <v>1045</v>
       </c>
     </row>
@@ -10944,13 +11300,13 @@
       <c r="I186" s="1">
         <v>0</v>
       </c>
-      <c r="J186" s="14" t="s">
+      <c r="J186" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K186" s="14" t="s">
+      <c r="K186" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L186" s="13" t="s">
+      <c r="L186" s="12" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -10976,13 +11332,13 @@
       <c r="I187" s="1">
         <v>0</v>
       </c>
-      <c r="J187" s="14" t="s">
+      <c r="J187" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K187" s="14" t="s">
+      <c r="K187" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L187" s="13" t="s">
+      <c r="L187" s="12" t="s">
         <v>1056</v>
       </c>
     </row>
@@ -11008,13 +11364,13 @@
       <c r="I188" s="1">
         <v>0</v>
       </c>
-      <c r="J188" s="14" t="s">
+      <c r="J188" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K188" s="14" t="s">
+      <c r="K188" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L188" s="13" t="s">
+      <c r="L188" s="12" t="s">
         <v>1061</v>
       </c>
     </row>
@@ -11040,13 +11396,13 @@
       <c r="I189" s="1">
         <v>0</v>
       </c>
-      <c r="J189" s="14" t="s">
+      <c r="J189" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K189" s="14" t="s">
+      <c r="K189" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L189" s="13" t="s">
+      <c r="L189" s="12" t="s">
         <v>1066</v>
       </c>
     </row>
@@ -11072,13 +11428,13 @@
       <c r="I190" s="1">
         <v>0</v>
       </c>
-      <c r="J190" s="14" t="s">
+      <c r="J190" s="13" t="s">
         <v>1050</v>
       </c>
-      <c r="K190" s="14" t="s">
+      <c r="K190" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L190" s="13" t="s">
+      <c r="L190" s="12" t="s">
         <v>1071</v>
       </c>
     </row>
@@ -11095,7 +11451,7 @@
       <c r="F191" s="1">
         <v>5</v>
       </c>
-      <c r="G191" s="8" t="s">
+      <c r="G191" s="7" t="s">
         <v>1074</v>
       </c>
       <c r="H191" s="1" t="s">
@@ -11104,13 +11460,13 @@
       <c r="I191" s="1">
         <v>0</v>
       </c>
-      <c r="J191" s="14" t="s">
+      <c r="J191" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K191" s="14" t="s">
+      <c r="K191" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L191" s="13" t="s">
+      <c r="L191" s="12" t="s">
         <v>1077</v>
       </c>
     </row>
@@ -11127,7 +11483,7 @@
       <c r="F192" s="1">
         <v>5</v>
       </c>
-      <c r="G192" s="8" t="s">
+      <c r="G192" s="7" t="s">
         <v>1080</v>
       </c>
       <c r="H192" s="1" t="s">
@@ -11136,13 +11492,13 @@
       <c r="I192" s="1">
         <v>0</v>
       </c>
-      <c r="J192" s="14" t="s">
+      <c r="J192" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K192" s="14" t="s">
+      <c r="K192" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L192" s="13" t="s">
+      <c r="L192" s="12" t="s">
         <v>1082</v>
       </c>
     </row>
@@ -11159,7 +11515,7 @@
       <c r="F193" s="1">
         <v>5</v>
       </c>
-      <c r="G193" s="8" t="s">
+      <c r="G193" s="7" t="s">
         <v>1085</v>
       </c>
       <c r="H193" s="1" t="s">
@@ -11168,13 +11524,13 @@
       <c r="I193" s="1">
         <v>0</v>
       </c>
-      <c r="J193" s="14" t="s">
+      <c r="J193" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K193" s="14" t="s">
+      <c r="K193" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L193" s="13" t="s">
+      <c r="L193" s="12" t="s">
         <v>1087</v>
       </c>
     </row>
@@ -11191,7 +11547,7 @@
       <c r="F194" s="1">
         <v>5</v>
       </c>
-      <c r="G194" s="8" t="s">
+      <c r="G194" s="7" t="s">
         <v>1090</v>
       </c>
       <c r="H194" s="1" t="s">
@@ -11200,13 +11556,13 @@
       <c r="I194" s="1">
         <v>0</v>
       </c>
-      <c r="J194" s="14" t="s">
+      <c r="J194" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K194" s="14" t="s">
+      <c r="K194" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L194" s="13" t="s">
+      <c r="L194" s="12" t="s">
         <v>1092</v>
       </c>
     </row>
@@ -11223,7 +11579,7 @@
       <c r="F195" s="1">
         <v>5</v>
       </c>
-      <c r="G195" s="8" t="s">
+      <c r="G195" s="7" t="s">
         <v>1095</v>
       </c>
       <c r="H195" s="1" t="s">
@@ -11232,45 +11588,45 @@
       <c r="I195" s="1">
         <v>0</v>
       </c>
-      <c r="J195" s="14" t="s">
+      <c r="J195" s="13" t="s">
         <v>1076</v>
       </c>
-      <c r="K195" s="14" t="s">
+      <c r="K195" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L195" s="13" t="s">
+      <c r="L195" s="12" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="196" s="4" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C196" s="4" t="s">
+    <row r="196" s="9" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C196" s="9" t="s">
         <v>1098</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D196" s="9" t="s">
         <v>1099</v>
       </c>
-      <c r="E196" s="4">
+      <c r="E196" s="9">
         <v>5</v>
       </c>
-      <c r="F196" s="4">
+      <c r="F196" s="9">
         <v>5</v>
       </c>
-      <c r="G196" s="9" t="s">
+      <c r="G196" s="11" t="s">
         <v>1100</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="I196" s="4">
-        <v>0</v>
-      </c>
-      <c r="J196" s="16" t="s">
+      <c r="I196" s="9">
+        <v>0</v>
+      </c>
+      <c r="J196" s="15" t="s">
         <v>1102</v>
       </c>
-      <c r="K196" s="16" t="s">
+      <c r="K196" s="15" t="s">
         <v>1020</v>
       </c>
-      <c r="L196" s="16" t="s">
+      <c r="L196" s="15" t="s">
         <v>1103</v>
       </c>
     </row>
@@ -11287,7 +11643,7 @@
       <c r="F197" s="1">
         <v>5</v>
       </c>
-      <c r="G197" s="8" t="s">
+      <c r="G197" s="7" t="s">
         <v>1106</v>
       </c>
       <c r="H197" s="1" t="s">
@@ -11296,13 +11652,13 @@
       <c r="I197" s="1">
         <v>0</v>
       </c>
-      <c r="J197" s="14" t="s">
+      <c r="J197" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K197" s="14" t="s">
+      <c r="K197" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L197" s="13" t="s">
+      <c r="L197" s="12" t="s">
         <v>1108</v>
       </c>
     </row>
@@ -11319,7 +11675,7 @@
       <c r="F198" s="1">
         <v>5</v>
       </c>
-      <c r="G198" s="8" t="s">
+      <c r="G198" s="7" t="s">
         <v>1111</v>
       </c>
       <c r="H198" s="1" t="s">
@@ -11328,13 +11684,13 @@
       <c r="I198" s="1">
         <v>0</v>
       </c>
-      <c r="J198" s="14" t="s">
+      <c r="J198" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K198" s="14" t="s">
+      <c r="K198" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L198" s="13" t="s">
+      <c r="L198" s="12" t="s">
         <v>1113</v>
       </c>
     </row>
@@ -11351,7 +11707,7 @@
       <c r="F199" s="1">
         <v>5</v>
       </c>
-      <c r="G199" s="8" t="s">
+      <c r="G199" s="7" t="s">
         <v>1116</v>
       </c>
       <c r="H199" s="1" t="s">
@@ -11360,13 +11716,13 @@
       <c r="I199" s="1">
         <v>0</v>
       </c>
-      <c r="J199" s="14" t="s">
+      <c r="J199" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K199" s="14" t="s">
+      <c r="K199" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L199" s="13" t="s">
+      <c r="L199" s="12" t="s">
         <v>1118</v>
       </c>
     </row>
@@ -11383,7 +11739,7 @@
       <c r="F200" s="1">
         <v>5</v>
       </c>
-      <c r="G200" s="8" t="s">
+      <c r="G200" s="7" t="s">
         <v>1121</v>
       </c>
       <c r="H200" s="1" t="s">
@@ -11392,13 +11748,13 @@
       <c r="I200" s="1">
         <v>0</v>
       </c>
-      <c r="J200" s="14" t="s">
+      <c r="J200" s="13" t="s">
         <v>1102</v>
       </c>
-      <c r="K200" s="14" t="s">
+      <c r="K200" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L200" s="13" t="s">
+      <c r="L200" s="12" t="s">
         <v>1123</v>
       </c>
     </row>
@@ -11406,7 +11762,7 @@
       <c r="C201" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="D201" s="2" t="s">
+      <c r="D201" s="5" t="s">
         <v>1125</v>
       </c>
       <c r="E201" s="1">
@@ -11415,7 +11771,7 @@
       <c r="F201" s="1">
         <v>5</v>
       </c>
-      <c r="G201" s="8" t="s">
+      <c r="G201" s="7" t="s">
         <v>1126</v>
       </c>
       <c r="H201" s="1" t="s">
@@ -11424,13 +11780,13 @@
       <c r="I201" s="1">
         <v>0</v>
       </c>
-      <c r="J201" s="14" t="s">
+      <c r="J201" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K201" s="14" t="s">
+      <c r="K201" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L201" s="13" t="s">
+      <c r="L201" s="12" t="s">
         <v>1129</v>
       </c>
     </row>
@@ -11438,7 +11794,7 @@
       <c r="C202" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="D202" s="2" t="s">
+      <c r="D202" s="5" t="s">
         <v>1131</v>
       </c>
       <c r="E202" s="1">
@@ -11447,7 +11803,7 @@
       <c r="F202" s="1">
         <v>5</v>
       </c>
-      <c r="G202" s="8" t="s">
+      <c r="G202" s="7" t="s">
         <v>1132</v>
       </c>
       <c r="H202" s="1" t="s">
@@ -11456,13 +11812,13 @@
       <c r="I202" s="1">
         <v>0</v>
       </c>
-      <c r="J202" s="14" t="s">
+      <c r="J202" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K202" s="14" t="s">
+      <c r="K202" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L202" s="13" t="s">
+      <c r="L202" s="12" t="s">
         <v>1134</v>
       </c>
     </row>
@@ -11470,7 +11826,7 @@
       <c r="C203" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="D203" s="5" t="s">
         <v>1136</v>
       </c>
       <c r="E203" s="1">
@@ -11479,7 +11835,7 @@
       <c r="F203" s="1">
         <v>5</v>
       </c>
-      <c r="G203" s="8" t="s">
+      <c r="G203" s="7" t="s">
         <v>1137</v>
       </c>
       <c r="H203" s="1" t="s">
@@ -11488,13 +11844,13 @@
       <c r="I203" s="1">
         <v>0</v>
       </c>
-      <c r="J203" s="14" t="s">
+      <c r="J203" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K203" s="14" t="s">
+      <c r="K203" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L203" s="13" t="s">
+      <c r="L203" s="12" t="s">
         <v>1139</v>
       </c>
     </row>
@@ -11502,7 +11858,7 @@
       <c r="C204" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="D204" s="2" t="s">
+      <c r="D204" s="5" t="s">
         <v>1141</v>
       </c>
       <c r="E204" s="1">
@@ -11511,7 +11867,7 @@
       <c r="F204" s="1">
         <v>5</v>
       </c>
-      <c r="G204" s="8" t="s">
+      <c r="G204" s="7" t="s">
         <v>1142</v>
       </c>
       <c r="H204" s="1" t="s">
@@ -11520,13 +11876,13 @@
       <c r="I204" s="1">
         <v>0</v>
       </c>
-      <c r="J204" s="14" t="s">
+      <c r="J204" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K204" s="14" t="s">
+      <c r="K204" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L204" s="13" t="s">
+      <c r="L204" s="12" t="s">
         <v>1144</v>
       </c>
     </row>
@@ -11534,7 +11890,7 @@
       <c r="C205" s="1" t="s">
         <v>1145</v>
       </c>
-      <c r="D205" s="2" t="s">
+      <c r="D205" s="5" t="s">
         <v>1146</v>
       </c>
       <c r="E205" s="1">
@@ -11543,7 +11899,7 @@
       <c r="F205" s="1">
         <v>5</v>
       </c>
-      <c r="G205" s="8" t="s">
+      <c r="G205" s="7" t="s">
         <v>1147</v>
       </c>
       <c r="H205" s="1" t="s">
@@ -11552,13 +11908,13 @@
       <c r="I205" s="1">
         <v>0</v>
       </c>
-      <c r="J205" s="14" t="s">
+      <c r="J205" s="13" t="s">
         <v>1128</v>
       </c>
-      <c r="K205" s="14" t="s">
+      <c r="K205" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L205" s="13" t="s">
+      <c r="L205" s="12" t="s">
         <v>1149</v>
       </c>
     </row>
@@ -11575,7 +11931,7 @@
       <c r="F206" s="1">
         <v>5</v>
       </c>
-      <c r="G206" s="8" t="s">
+      <c r="G206" s="7" t="s">
         <v>1152</v>
       </c>
       <c r="H206" s="1" t="s">
@@ -11584,13 +11940,13 @@
       <c r="I206" s="1">
         <v>0</v>
       </c>
-      <c r="J206" s="14" t="s">
+      <c r="J206" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K206" s="14" t="s">
+      <c r="K206" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L206" s="13" t="s">
+      <c r="L206" s="12" t="s">
         <v>1155</v>
       </c>
     </row>
@@ -11607,7 +11963,7 @@
       <c r="F207" s="1">
         <v>5</v>
       </c>
-      <c r="G207" s="8" t="s">
+      <c r="G207" s="7" t="s">
         <v>1158</v>
       </c>
       <c r="H207" s="1" t="s">
@@ -11616,13 +11972,13 @@
       <c r="I207" s="1">
         <v>0</v>
       </c>
-      <c r="J207" s="14" t="s">
+      <c r="J207" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K207" s="14" t="s">
+      <c r="K207" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L207" s="13" t="s">
+      <c r="L207" s="12" t="s">
         <v>1160</v>
       </c>
     </row>
@@ -11639,7 +11995,7 @@
       <c r="F208" s="1">
         <v>5</v>
       </c>
-      <c r="G208" s="8" t="s">
+      <c r="G208" s="7" t="s">
         <v>1163</v>
       </c>
       <c r="H208" s="1" t="s">
@@ -11648,13 +12004,13 @@
       <c r="I208" s="1">
         <v>0</v>
       </c>
-      <c r="J208" s="14" t="s">
+      <c r="J208" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K208" s="14" t="s">
+      <c r="K208" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L208" s="13" t="s">
+      <c r="L208" s="12" t="s">
         <v>1165</v>
       </c>
     </row>
@@ -11671,7 +12027,7 @@
       <c r="F209" s="1">
         <v>5</v>
       </c>
-      <c r="G209" s="8" t="s">
+      <c r="G209" s="7" t="s">
         <v>1168</v>
       </c>
       <c r="H209" s="1" t="s">
@@ -11680,13 +12036,13 @@
       <c r="I209" s="1">
         <v>0</v>
       </c>
-      <c r="J209" s="14" t="s">
+      <c r="J209" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K209" s="14" t="s">
+      <c r="K209" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L209" s="13" t="s">
+      <c r="L209" s="12" t="s">
         <v>1170</v>
       </c>
     </row>
@@ -11703,7 +12059,7 @@
       <c r="F210" s="1">
         <v>5</v>
       </c>
-      <c r="G210" s="8" t="s">
+      <c r="G210" s="7" t="s">
         <v>1173</v>
       </c>
       <c r="H210" s="1" t="s">
@@ -11712,13 +12068,13 @@
       <c r="I210" s="1">
         <v>0</v>
       </c>
-      <c r="J210" s="14" t="s">
+      <c r="J210" s="13" t="s">
         <v>1154</v>
       </c>
-      <c r="K210" s="14" t="s">
+      <c r="K210" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L210" s="13" t="s">
+      <c r="L210" s="12" t="s">
         <v>1175</v>
       </c>
     </row>
@@ -11735,7 +12091,7 @@
       <c r="F211" s="1">
         <v>5</v>
       </c>
-      <c r="G211" s="8" t="s">
+      <c r="G211" s="7" t="s">
         <v>1178</v>
       </c>
       <c r="H211" s="1" t="s">
@@ -11744,13 +12100,13 @@
       <c r="I211" s="1">
         <v>0</v>
       </c>
-      <c r="J211" s="14" t="s">
+      <c r="J211" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K211" s="14" t="s">
+      <c r="K211" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L211" s="13" t="s">
+      <c r="L211" s="12" t="s">
         <v>1181</v>
       </c>
     </row>
@@ -11767,7 +12123,7 @@
       <c r="F212" s="1">
         <v>5</v>
       </c>
-      <c r="G212" s="8" t="s">
+      <c r="G212" s="7" t="s">
         <v>1184</v>
       </c>
       <c r="H212" s="1" t="s">
@@ -11776,13 +12132,13 @@
       <c r="I212" s="1">
         <v>0</v>
       </c>
-      <c r="J212" s="14" t="s">
+      <c r="J212" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K212" s="14" t="s">
+      <c r="K212" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L212" s="13" t="s">
+      <c r="L212" s="12" t="s">
         <v>1186</v>
       </c>
     </row>
@@ -11799,7 +12155,7 @@
       <c r="F213" s="1">
         <v>5</v>
       </c>
-      <c r="G213" s="8" t="s">
+      <c r="G213" s="7" t="s">
         <v>1189</v>
       </c>
       <c r="H213" s="1" t="s">
@@ -11808,19 +12164,19 @@
       <c r="I213" s="1">
         <v>0</v>
       </c>
-      <c r="J213" s="14" t="s">
+      <c r="J213" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K213" s="14" t="s">
+      <c r="K213" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L213" s="13" t="s">
+      <c r="L213" s="12" t="s">
         <v>1191</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
+      <c r="A214" s="5"/>
+      <c r="B214" s="5"/>
       <c r="C214" s="1" t="s">
         <v>1192</v>
       </c>
@@ -11833,7 +12189,7 @@
       <c r="F214" s="1">
         <v>5</v>
       </c>
-      <c r="G214" s="8" t="s">
+      <c r="G214" s="7" t="s">
         <v>1194</v>
       </c>
       <c r="H214" s="1" t="s">
@@ -11842,19 +12198,19 @@
       <c r="I214" s="1">
         <v>0</v>
       </c>
-      <c r="J214" s="14" t="s">
+      <c r="J214" s="13" t="s">
         <v>1180</v>
       </c>
-      <c r="K214" s="14" t="s">
+      <c r="K214" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="L214" s="13" t="s">
+      <c r="L214" s="12" t="s">
         <v>1196</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A215" s="2"/>
-      <c r="B215" s="2"/>
+      <c r="A215" s="5"/>
+      <c r="B215" s="5"/>
       <c r="C215" s="1" t="s">
         <v>1197</v>
       </c>
@@ -11867,7 +12223,7 @@
       <c r="F215" s="1">
         <v>5</v>
       </c>
-      <c r="G215" s="8" t="s">
+      <c r="G215" s="7" t="s">
         <v>1199</v>
       </c>
       <c r="H215" s="1" t="s">
@@ -11876,69 +12232,69 @@
       <c r="I215" s="1">
         <v>0</v>
       </c>
-      <c r="J215" s="14" t="s">
+      <c r="J215" s="13" t="s">
         <v>1201</v>
       </c>
-      <c r="K215" s="14" t="s">
+      <c r="K215" s="13" t="s">
         <v>1202</v>
       </c>
-      <c r="L215" s="13" t="s">
+      <c r="L215" s="12" t="s">
         <v>1203</v>
       </c>
     </row>
-    <row r="216" s="3" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A216" s="2"/>
-      <c r="B216" s="2"/>
+    <row r="216" s="2" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A216" s="5"/>
+      <c r="B216" s="5"/>
       <c r="C216" s="1">
         <v>1210</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="D216" s="2" t="s">
         <v>1204</v>
       </c>
-      <c r="E216" s="3">
+      <c r="E216" s="2">
         <v>6</v>
       </c>
-      <c r="F216" s="3">
+      <c r="F216" s="2">
         <v>6</v>
       </c>
-      <c r="G216" s="10" t="s">
+      <c r="G216" s="6" t="s">
         <v>1205</v>
       </c>
-      <c r="H216" s="3" t="s">
+      <c r="H216" s="2" t="s">
         <v>1206</v>
       </c>
-      <c r="I216" s="3">
-        <v>0</v>
-      </c>
-      <c r="J216" s="15" t="s">
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
+      <c r="J216" s="14" t="s">
         <v>1207</v>
       </c>
-      <c r="K216" s="15" t="s">
+      <c r="K216" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L216" s="13" t="s">
+      <c r="L216" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="M216" s="3" t="s">
+      <c r="M216" s="2" t="s">
         <v>1210</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:13">
-      <c r="A217" s="2"/>
-      <c r="B217" s="2"/>
+      <c r="A217" s="5"/>
+      <c r="B217" s="5"/>
       <c r="C217" s="1">
         <v>1211</v>
       </c>
-      <c r="D217" s="2" t="s">
+      <c r="D217" s="5" t="s">
         <v>1211</v>
       </c>
-      <c r="E217" s="2">
+      <c r="E217" s="5">
         <v>6</v>
       </c>
-      <c r="F217" s="2">
+      <c r="F217" s="5">
         <v>6</v>
       </c>
-      <c r="G217" s="8" t="s">
+      <c r="G217" s="7" t="s">
         <v>1212</v>
       </c>
       <c r="H217" s="1" t="s">
@@ -11947,32 +12303,32 @@
       <c r="I217" s="1">
         <v>0</v>
       </c>
-      <c r="J217" s="14" t="s">
+      <c r="J217" s="13" t="s">
         <v>1214</v>
       </c>
-      <c r="K217" s="14" t="s">
+      <c r="K217" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L217" s="13" t="s">
+      <c r="L217" s="12" t="s">
         <v>1215</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:13">
-      <c r="A218" s="2"/>
-      <c r="B218" s="2"/>
+      <c r="A218" s="5"/>
+      <c r="B218" s="5"/>
       <c r="C218" s="1">
         <v>1212</v>
       </c>
-      <c r="D218" s="2" t="s">
+      <c r="D218" s="5" t="s">
         <v>1216</v>
       </c>
-      <c r="E218" s="2">
+      <c r="E218" s="5">
         <v>6</v>
       </c>
-      <c r="F218" s="2">
+      <c r="F218" s="5">
         <v>6</v>
       </c>
-      <c r="G218" s="8" t="s">
+      <c r="G218" s="7" t="s">
         <v>1217</v>
       </c>
       <c r="H218" s="1" t="s">
@@ -11981,32 +12337,32 @@
       <c r="I218" s="1">
         <v>0</v>
       </c>
-      <c r="J218" s="14" t="s">
+      <c r="J218" s="13" t="s">
         <v>1219</v>
       </c>
-      <c r="K218" s="14" t="s">
+      <c r="K218" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L218" s="13" t="s">
+      <c r="L218" s="12" t="s">
         <v>1220</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:13">
-      <c r="A219" s="2"/>
-      <c r="B219" s="2"/>
+      <c r="A219" s="5"/>
+      <c r="B219" s="5"/>
       <c r="C219" s="1">
         <v>1213</v>
       </c>
-      <c r="D219" s="2" t="s">
+      <c r="D219" s="5" t="s">
         <v>1221</v>
       </c>
-      <c r="E219" s="2">
+      <c r="E219" s="5">
         <v>6</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="5">
         <v>6</v>
       </c>
-      <c r="G219" s="8" t="s">
+      <c r="G219" s="7" t="s">
         <v>1222</v>
       </c>
       <c r="H219" s="1" t="s">
@@ -12015,32 +12371,32 @@
       <c r="I219" s="1">
         <v>0</v>
       </c>
-      <c r="J219" s="14" t="s">
+      <c r="J219" s="13" t="s">
         <v>1224</v>
       </c>
-      <c r="K219" s="14" t="s">
+      <c r="K219" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L219" s="13" t="s">
+      <c r="L219" s="12" t="s">
         <v>1225</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:13">
-      <c r="A220" s="2"/>
-      <c r="B220" s="2"/>
+      <c r="A220" s="5"/>
+      <c r="B220" s="5"/>
       <c r="C220" s="1">
         <v>1214</v>
       </c>
-      <c r="D220" s="2" t="s">
+      <c r="D220" s="5" t="s">
         <v>1226</v>
       </c>
-      <c r="E220" s="2">
+      <c r="E220" s="5">
         <v>6</v>
       </c>
-      <c r="F220" s="2">
+      <c r="F220" s="5">
         <v>6</v>
       </c>
-      <c r="G220" s="8" t="s">
+      <c r="G220" s="7" t="s">
         <v>1227</v>
       </c>
       <c r="H220" s="1" t="s">
@@ -12049,47 +12405,47 @@
       <c r="I220" s="1">
         <v>0</v>
       </c>
-      <c r="J220" s="14" t="s">
+      <c r="J220" s="13" t="s">
         <v>1229</v>
       </c>
-      <c r="K220" s="14" t="s">
+      <c r="K220" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L220" s="13" t="s">
+      <c r="L220" s="12" t="s">
         <v>1230</v>
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:13">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
+      <c r="A221" s="5"/>
+      <c r="B221" s="5"/>
       <c r="C221" s="1">
         <v>1215</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="D221" s="5" t="s">
         <v>1231</v>
       </c>
-      <c r="E221" s="2">
+      <c r="E221" s="5">
         <v>6</v>
       </c>
-      <c r="F221" s="2">
+      <c r="F221" s="5">
         <v>6</v>
       </c>
-      <c r="G221" s="10" t="s">
+      <c r="G221" s="6" t="s">
         <v>1232</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="I221" s="3">
-        <v>0</v>
-      </c>
-      <c r="J221" s="14" t="s">
+      <c r="I221" s="2">
+        <v>0</v>
+      </c>
+      <c r="J221" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K221" s="15" t="s">
+      <c r="K221" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L221" s="13" t="s">
+      <c r="L221" s="12" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -12097,16 +12453,16 @@
       <c r="C222" s="1">
         <v>1216</v>
       </c>
-      <c r="D222" s="2" t="s">
+      <c r="D222" s="5" t="s">
         <v>1236</v>
       </c>
-      <c r="E222" s="2">
+      <c r="E222" s="5">
         <v>6</v>
       </c>
-      <c r="F222" s="2">
+      <c r="F222" s="5">
         <v>6</v>
       </c>
-      <c r="G222" s="11" t="s">
+      <c r="G222" s="8" t="s">
         <v>1237</v>
       </c>
       <c r="H222" s="1" t="s">
@@ -12115,13 +12471,13 @@
       <c r="I222" s="1">
         <v>0</v>
       </c>
-      <c r="J222" s="14" t="s">
+      <c r="J222" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K222" s="14" t="s">
+      <c r="K222" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L222" s="13" t="s">
+      <c r="L222" s="12" t="s">
         <v>1239</v>
       </c>
     </row>
@@ -12129,16 +12485,16 @@
       <c r="C223" s="1">
         <v>1217</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="D223" s="5" t="s">
         <v>1240</v>
       </c>
-      <c r="E223" s="2">
+      <c r="E223" s="5">
         <v>6</v>
       </c>
-      <c r="F223" s="2">
+      <c r="F223" s="5">
         <v>6</v>
       </c>
-      <c r="G223" s="11" t="s">
+      <c r="G223" s="8" t="s">
         <v>1241</v>
       </c>
       <c r="H223" s="1" t="s">
@@ -12147,13 +12503,13 @@
       <c r="I223" s="1">
         <v>0</v>
       </c>
-      <c r="J223" s="14" t="s">
+      <c r="J223" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K223" s="14" t="s">
+      <c r="K223" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L223" s="13" t="s">
+      <c r="L223" s="12" t="s">
         <v>1243</v>
       </c>
     </row>
@@ -12161,16 +12517,16 @@
       <c r="C224" s="1">
         <v>1218</v>
       </c>
-      <c r="D224" s="2" t="s">
+      <c r="D224" s="5" t="s">
         <v>1244</v>
       </c>
-      <c r="E224" s="2">
+      <c r="E224" s="5">
         <v>6</v>
       </c>
-      <c r="F224" s="2">
+      <c r="F224" s="5">
         <v>6</v>
       </c>
-      <c r="G224" s="11" t="s">
+      <c r="G224" s="8" t="s">
         <v>1245</v>
       </c>
       <c r="H224" s="1" t="s">
@@ -12179,13 +12535,13 @@
       <c r="I224" s="1">
         <v>0</v>
       </c>
-      <c r="J224" s="14" t="s">
+      <c r="J224" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K224" s="14" t="s">
+      <c r="K224" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L224" s="13" t="s">
+      <c r="L224" s="12" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -12193,16 +12549,16 @@
       <c r="C225" s="1">
         <v>1219</v>
       </c>
-      <c r="D225" s="2" t="s">
+      <c r="D225" s="5" t="s">
         <v>1248</v>
       </c>
-      <c r="E225" s="2">
+      <c r="E225" s="5">
         <v>6</v>
       </c>
-      <c r="F225" s="2">
+      <c r="F225" s="5">
         <v>6</v>
       </c>
-      <c r="G225" s="11" t="s">
+      <c r="G225" s="8" t="s">
         <v>1249</v>
       </c>
       <c r="H225" s="1" t="s">
@@ -12211,13 +12567,13 @@
       <c r="I225" s="1">
         <v>0</v>
       </c>
-      <c r="J225" s="14" t="s">
+      <c r="J225" s="13" t="s">
         <v>1234</v>
       </c>
-      <c r="K225" s="14" t="s">
+      <c r="K225" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L225" s="13" t="s">
+      <c r="L225" s="12" t="s">
         <v>1251</v>
       </c>
     </row>
@@ -12225,31 +12581,31 @@
       <c r="C226" s="1">
         <v>1220</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="D226" s="5" t="s">
         <v>1252</v>
       </c>
-      <c r="E226" s="2">
+      <c r="E226" s="5">
         <v>6</v>
       </c>
-      <c r="F226" s="2">
+      <c r="F226" s="5">
         <v>6</v>
       </c>
-      <c r="G226" s="11" t="s">
+      <c r="G226" s="8" t="s">
         <v>1253</v>
       </c>
       <c r="H226" s="1" t="s">
         <v>1254</v>
       </c>
-      <c r="I226" s="3">
-        <v>0</v>
-      </c>
-      <c r="J226" s="14" t="s">
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
+      <c r="J226" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="K226" s="15" t="s">
+      <c r="K226" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L226" s="13" t="s">
+      <c r="L226" s="12" t="s">
         <v>1256</v>
       </c>
     </row>
@@ -12257,16 +12613,16 @@
       <c r="C227" s="1">
         <v>1221</v>
       </c>
-      <c r="D227" s="2" t="s">
+      <c r="D227" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="E227" s="2">
+      <c r="E227" s="5">
         <v>6</v>
       </c>
-      <c r="F227" s="2">
+      <c r="F227" s="5">
         <v>6</v>
       </c>
-      <c r="G227" s="11" t="s">
+      <c r="G227" s="8" t="s">
         <v>1258</v>
       </c>
       <c r="H227" s="1" t="s">
@@ -12275,13 +12631,13 @@
       <c r="I227" s="1">
         <v>0</v>
       </c>
-      <c r="J227" s="14" t="s">
+      <c r="J227" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="K227" s="14" t="s">
+      <c r="K227" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L227" s="13" t="s">
+      <c r="L227" s="12" t="s">
         <v>1260</v>
       </c>
     </row>
@@ -12289,16 +12645,16 @@
       <c r="C228" s="1">
         <v>1222</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="D228" s="5" t="s">
         <v>1261</v>
       </c>
-      <c r="E228" s="2">
+      <c r="E228" s="5">
         <v>6</v>
       </c>
-      <c r="F228" s="2">
+      <c r="F228" s="5">
         <v>6</v>
       </c>
-      <c r="G228" s="11" t="s">
+      <c r="G228" s="8" t="s">
         <v>1262</v>
       </c>
       <c r="H228" s="1" t="s">
@@ -12307,13 +12663,13 @@
       <c r="I228" s="1">
         <v>0</v>
       </c>
-      <c r="J228" s="14" t="s">
+      <c r="J228" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="K228" s="14" t="s">
+      <c r="K228" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L228" s="13" t="s">
+      <c r="L228" s="12" t="s">
         <v>1264</v>
       </c>
     </row>
@@ -12321,16 +12677,16 @@
       <c r="C229" s="1">
         <v>1223</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="D229" s="5" t="s">
         <v>1265</v>
       </c>
-      <c r="E229" s="2">
+      <c r="E229" s="5">
         <v>6</v>
       </c>
-      <c r="F229" s="2">
+      <c r="F229" s="5">
         <v>6</v>
       </c>
-      <c r="G229" s="11" t="s">
+      <c r="G229" s="8" t="s">
         <v>1266</v>
       </c>
       <c r="H229" s="1" t="s">
@@ -12339,13 +12695,13 @@
       <c r="I229" s="1">
         <v>0</v>
       </c>
-      <c r="J229" s="14" t="s">
+      <c r="J229" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="K229" s="14" t="s">
+      <c r="K229" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L229" s="13" t="s">
+      <c r="L229" s="12" t="s">
         <v>1268</v>
       </c>
     </row>
@@ -12353,16 +12709,16 @@
       <c r="C230" s="1">
         <v>1224</v>
       </c>
-      <c r="D230" s="2" t="s">
+      <c r="D230" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="5">
         <v>6</v>
       </c>
-      <c r="F230" s="2">
+      <c r="F230" s="5">
         <v>6</v>
       </c>
-      <c r="G230" s="11" t="s">
+      <c r="G230" s="8" t="s">
         <v>1270</v>
       </c>
       <c r="H230" s="1" t="s">
@@ -12371,13 +12727,13 @@
       <c r="I230" s="1">
         <v>0</v>
       </c>
-      <c r="J230" s="14" t="s">
+      <c r="J230" s="13" t="s">
         <v>1255</v>
       </c>
-      <c r="K230" s="14" t="s">
+      <c r="K230" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L230" s="13" t="s">
+      <c r="L230" s="12" t="s">
         <v>1272</v>
       </c>
     </row>
@@ -12385,31 +12741,31 @@
       <c r="C231" s="1">
         <v>1225</v>
       </c>
-      <c r="D231" s="2" t="s">
+      <c r="D231" s="5" t="s">
         <v>1273</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="5">
         <v>6</v>
       </c>
-      <c r="F231" s="2">
+      <c r="F231" s="5">
         <v>6</v>
       </c>
-      <c r="G231" s="11" t="s">
+      <c r="G231" s="8" t="s">
         <v>1274</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="I231" s="3">
-        <v>0</v>
-      </c>
-      <c r="J231" s="14" t="s">
+      <c r="I231" s="2">
+        <v>0</v>
+      </c>
+      <c r="J231" s="13" t="s">
         <v>1276</v>
       </c>
-      <c r="K231" s="15" t="s">
+      <c r="K231" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L231" s="13" t="s">
+      <c r="L231" s="12" t="s">
         <v>1277</v>
       </c>
     </row>
@@ -12417,16 +12773,16 @@
       <c r="C232" s="1">
         <v>1226</v>
       </c>
-      <c r="D232" s="2" t="s">
+      <c r="D232" s="5" t="s">
         <v>1278</v>
       </c>
-      <c r="E232" s="2">
+      <c r="E232" s="5">
         <v>6</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="5">
         <v>6</v>
       </c>
-      <c r="G232" s="11" t="s">
+      <c r="G232" s="8" t="s">
         <v>1279</v>
       </c>
       <c r="H232" s="1" t="s">
@@ -12435,13 +12791,13 @@
       <c r="I232" s="1">
         <v>0</v>
       </c>
-      <c r="J232" s="14" t="s">
+      <c r="J232" s="13" t="s">
         <v>1276</v>
       </c>
-      <c r="K232" s="14" t="s">
+      <c r="K232" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L232" s="13" t="s">
+      <c r="L232" s="12" t="s">
         <v>1281</v>
       </c>
     </row>
@@ -12449,16 +12805,16 @@
       <c r="C233" s="1">
         <v>1227</v>
       </c>
-      <c r="D233" s="2" t="s">
+      <c r="D233" s="5" t="s">
         <v>1282</v>
       </c>
-      <c r="E233" s="2">
+      <c r="E233" s="5">
         <v>6</v>
       </c>
-      <c r="F233" s="2">
+      <c r="F233" s="5">
         <v>6</v>
       </c>
-      <c r="G233" s="11" t="s">
+      <c r="G233" s="8" t="s">
         <v>1283</v>
       </c>
       <c r="H233" s="1" t="s">
@@ -12467,13 +12823,13 @@
       <c r="I233" s="1">
         <v>0</v>
       </c>
-      <c r="J233" s="14" t="s">
+      <c r="J233" s="13" t="s">
         <v>1276</v>
       </c>
-      <c r="K233" s="14" t="s">
+      <c r="K233" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L233" s="13" t="s">
+      <c r="L233" s="12" t="s">
         <v>1285</v>
       </c>
     </row>
@@ -12481,16 +12837,16 @@
       <c r="C234" s="1">
         <v>1228</v>
       </c>
-      <c r="D234" s="2" t="s">
+      <c r="D234" s="5" t="s">
         <v>1286</v>
       </c>
-      <c r="E234" s="2">
+      <c r="E234" s="5">
         <v>6</v>
       </c>
-      <c r="F234" s="2">
+      <c r="F234" s="5">
         <v>6</v>
       </c>
-      <c r="G234" s="11" t="s">
+      <c r="G234" s="8" t="s">
         <v>1287</v>
       </c>
       <c r="H234" s="1" t="s">
@@ -12499,13 +12855,13 @@
       <c r="I234" s="1">
         <v>0</v>
       </c>
-      <c r="J234" s="14" t="s">
+      <c r="J234" s="13" t="s">
         <v>1276</v>
       </c>
-      <c r="K234" s="14" t="s">
+      <c r="K234" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L234" s="13" t="s">
+      <c r="L234" s="12" t="s">
         <v>1289</v>
       </c>
     </row>
@@ -12513,16 +12869,16 @@
       <c r="C235" s="1">
         <v>1229</v>
       </c>
-      <c r="D235" s="2" t="s">
+      <c r="D235" s="5" t="s">
         <v>1290</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="5">
         <v>6</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="5">
         <v>6</v>
       </c>
-      <c r="G235" s="11" t="s">
+      <c r="G235" s="8" t="s">
         <v>1291</v>
       </c>
       <c r="H235" s="1" t="s">
@@ -12531,13 +12887,13 @@
       <c r="I235" s="1">
         <v>0</v>
       </c>
-      <c r="J235" s="14" t="s">
+      <c r="J235" s="13" t="s">
         <v>1276</v>
       </c>
-      <c r="K235" s="14" t="s">
+      <c r="K235" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L235" s="13" t="s">
+      <c r="L235" s="12" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -12545,31 +12901,31 @@
       <c r="C236" s="1">
         <v>1230</v>
       </c>
-      <c r="D236" s="2" t="s">
+      <c r="D236" s="5" t="s">
         <v>1294</v>
       </c>
-      <c r="E236" s="2">
+      <c r="E236" s="5">
         <v>6</v>
       </c>
-      <c r="F236" s="2">
+      <c r="F236" s="5">
         <v>6</v>
       </c>
-      <c r="G236" s="11" t="s">
+      <c r="G236" s="8" t="s">
         <v>1295</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="I236" s="3">
-        <v>0</v>
-      </c>
-      <c r="J236" s="14" t="s">
+      <c r="I236" s="2">
+        <v>0</v>
+      </c>
+      <c r="J236" s="13" t="s">
         <v>1297</v>
       </c>
-      <c r="K236" s="15" t="s">
+      <c r="K236" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L236" s="13" t="s">
+      <c r="L236" s="12" t="s">
         <v>1298</v>
       </c>
     </row>
@@ -12577,16 +12933,16 @@
       <c r="C237" s="1">
         <v>1231</v>
       </c>
-      <c r="D237" s="2" t="s">
+      <c r="D237" s="5" t="s">
         <v>1299</v>
       </c>
-      <c r="E237" s="2">
+      <c r="E237" s="5">
         <v>6</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="5">
         <v>6</v>
       </c>
-      <c r="G237" s="11" t="s">
+      <c r="G237" s="8" t="s">
         <v>1300</v>
       </c>
       <c r="H237" s="1" t="s">
@@ -12595,13 +12951,13 @@
       <c r="I237" s="1">
         <v>0</v>
       </c>
-      <c r="J237" s="14" t="s">
+      <c r="J237" s="13" t="s">
         <v>1297</v>
       </c>
-      <c r="K237" s="14" t="s">
+      <c r="K237" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L237" s="13" t="s">
+      <c r="L237" s="12" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -12609,16 +12965,16 @@
       <c r="C238" s="1">
         <v>1232</v>
       </c>
-      <c r="D238" s="2" t="s">
+      <c r="D238" s="5" t="s">
         <v>1303</v>
       </c>
-      <c r="E238" s="2">
+      <c r="E238" s="5">
         <v>6</v>
       </c>
-      <c r="F238" s="2">
+      <c r="F238" s="5">
         <v>6</v>
       </c>
-      <c r="G238" s="11" t="s">
+      <c r="G238" s="8" t="s">
         <v>1304</v>
       </c>
       <c r="H238" s="1" t="s">
@@ -12627,13 +12983,13 @@
       <c r="I238" s="1">
         <v>0</v>
       </c>
-      <c r="J238" s="14" t="s">
+      <c r="J238" s="13" t="s">
         <v>1297</v>
       </c>
-      <c r="K238" s="14" t="s">
+      <c r="K238" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L238" s="13" t="s">
+      <c r="L238" s="12" t="s">
         <v>1306</v>
       </c>
     </row>
@@ -12641,16 +12997,16 @@
       <c r="C239" s="1">
         <v>1233</v>
       </c>
-      <c r="D239" s="2" t="s">
+      <c r="D239" s="5" t="s">
         <v>1307</v>
       </c>
-      <c r="E239" s="2">
+      <c r="E239" s="5">
         <v>6</v>
       </c>
-      <c r="F239" s="2">
+      <c r="F239" s="5">
         <v>6</v>
       </c>
-      <c r="G239" s="11" t="s">
+      <c r="G239" s="8" t="s">
         <v>1308</v>
       </c>
       <c r="H239" s="1" t="s">
@@ -12659,13 +13015,13 @@
       <c r="I239" s="1">
         <v>0</v>
       </c>
-      <c r="J239" s="14" t="s">
+      <c r="J239" s="13" t="s">
         <v>1297</v>
       </c>
-      <c r="K239" s="14" t="s">
+      <c r="K239" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L239" s="13" t="s">
+      <c r="L239" s="12" t="s">
         <v>1310</v>
       </c>
     </row>
@@ -12673,16 +13029,16 @@
       <c r="C240" s="1">
         <v>1234</v>
       </c>
-      <c r="D240" s="2" t="s">
+      <c r="D240" s="5" t="s">
         <v>1311</v>
       </c>
-      <c r="E240" s="2">
+      <c r="E240" s="5">
         <v>6</v>
       </c>
-      <c r="F240" s="2">
+      <c r="F240" s="5">
         <v>6</v>
       </c>
-      <c r="G240" s="11" t="s">
+      <c r="G240" s="8" t="s">
         <v>1312</v>
       </c>
       <c r="H240" s="1" t="s">
@@ -12691,13 +13047,13 @@
       <c r="I240" s="1">
         <v>0</v>
       </c>
-      <c r="J240" s="14" t="s">
+      <c r="J240" s="13" t="s">
         <v>1297</v>
       </c>
-      <c r="K240" s="14" t="s">
+      <c r="K240" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L240" s="13" t="s">
+      <c r="L240" s="12" t="s">
         <v>1314</v>
       </c>
     </row>
@@ -12705,31 +13061,31 @@
       <c r="C241" s="1">
         <v>1235</v>
       </c>
-      <c r="D241" s="2" t="s">
+      <c r="D241" s="5" t="s">
         <v>1315</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E241" s="5">
         <v>6</v>
       </c>
-      <c r="F241" s="2">
+      <c r="F241" s="5">
         <v>6</v>
       </c>
-      <c r="G241" s="11" t="s">
+      <c r="G241" s="8" t="s">
         <v>1316</v>
       </c>
       <c r="H241" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="I241" s="3">
-        <v>0</v>
-      </c>
-      <c r="J241" s="14" t="s">
+      <c r="I241" s="2">
+        <v>0</v>
+      </c>
+      <c r="J241" s="13" t="s">
         <v>1318</v>
       </c>
-      <c r="K241" s="15" t="s">
+      <c r="K241" s="14" t="s">
         <v>1208</v>
       </c>
-      <c r="L241" s="13" t="s">
+      <c r="L241" s="12" t="s">
         <v>1319</v>
       </c>
     </row>
@@ -12737,16 +13093,16 @@
       <c r="C242" s="1">
         <v>1236</v>
       </c>
-      <c r="D242" s="2" t="s">
+      <c r="D242" s="5" t="s">
         <v>1320</v>
       </c>
-      <c r="E242" s="2">
+      <c r="E242" s="5">
         <v>6</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="5">
         <v>6</v>
       </c>
-      <c r="G242" s="11" t="s">
+      <c r="G242" s="8" t="s">
         <v>1321</v>
       </c>
       <c r="H242" s="1" t="s">
@@ -12755,13 +13111,13 @@
       <c r="I242" s="1">
         <v>0</v>
       </c>
-      <c r="J242" s="14" t="s">
+      <c r="J242" s="13" t="s">
         <v>1318</v>
       </c>
-      <c r="K242" s="14" t="s">
+      <c r="K242" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L242" s="13" t="s">
+      <c r="L242" s="12" t="s">
         <v>1323</v>
       </c>
     </row>
@@ -12769,16 +13125,16 @@
       <c r="C243" s="1">
         <v>1237</v>
       </c>
-      <c r="D243" s="2" t="s">
+      <c r="D243" s="5" t="s">
         <v>1324</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E243" s="5">
         <v>6</v>
       </c>
-      <c r="F243" s="2">
+      <c r="F243" s="5">
         <v>6</v>
       </c>
-      <c r="G243" s="11" t="s">
+      <c r="G243" s="8" t="s">
         <v>1325</v>
       </c>
       <c r="H243" s="1" t="s">
@@ -12787,13 +13143,13 @@
       <c r="I243" s="1">
         <v>0</v>
       </c>
-      <c r="J243" s="14" t="s">
+      <c r="J243" s="13" t="s">
         <v>1318</v>
       </c>
-      <c r="K243" s="14" t="s">
+      <c r="K243" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L243" s="13" t="s">
+      <c r="L243" s="12" t="s">
         <v>1327</v>
       </c>
     </row>
@@ -12801,16 +13157,16 @@
       <c r="C244" s="1">
         <v>1238</v>
       </c>
-      <c r="D244" s="2" t="s">
+      <c r="D244" s="5" t="s">
         <v>1328</v>
       </c>
-      <c r="E244" s="2">
+      <c r="E244" s="5">
         <v>6</v>
       </c>
-      <c r="F244" s="2">
+      <c r="F244" s="5">
         <v>6</v>
       </c>
-      <c r="G244" s="11" t="s">
+      <c r="G244" s="8" t="s">
         <v>1329</v>
       </c>
       <c r="H244" s="1" t="s">
@@ -12819,13 +13175,13 @@
       <c r="I244" s="1">
         <v>0</v>
       </c>
-      <c r="J244" s="14" t="s">
+      <c r="J244" s="13" t="s">
         <v>1318</v>
       </c>
-      <c r="K244" s="14" t="s">
+      <c r="K244" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L244" s="13" t="s">
+      <c r="L244" s="12" t="s">
         <v>1331</v>
       </c>
     </row>
@@ -12833,16 +13189,16 @@
       <c r="C245" s="1">
         <v>1239</v>
       </c>
-      <c r="D245" s="2" t="s">
+      <c r="D245" s="5" t="s">
         <v>1332</v>
       </c>
-      <c r="E245" s="2">
+      <c r="E245" s="5">
         <v>6</v>
       </c>
-      <c r="F245" s="2">
+      <c r="F245" s="5">
         <v>6</v>
       </c>
-      <c r="G245" s="11" t="s">
+      <c r="G245" s="8" t="s">
         <v>1333</v>
       </c>
       <c r="H245" s="1" t="s">
@@ -12851,13 +13207,13 @@
       <c r="I245" s="1">
         <v>0</v>
       </c>
-      <c r="J245" s="14" t="s">
+      <c r="J245" s="13" t="s">
         <v>1318</v>
       </c>
-      <c r="K245" s="14" t="s">
+      <c r="K245" s="13" t="s">
         <v>1208</v>
       </c>
-      <c r="L245" s="13" t="s">
+      <c r="L245" s="12" t="s">
         <v>1335</v>
       </c>
     </row>
@@ -12865,31 +13221,31 @@
       <c r="C246" s="1">
         <v>1240</v>
       </c>
-      <c r="D246" s="2" t="s">
+      <c r="D246" s="5" t="s">
         <v>1336</v>
       </c>
-      <c r="E246" s="2">
+      <c r="E246" s="5">
         <v>6</v>
       </c>
-      <c r="F246" s="2">
+      <c r="F246" s="5">
         <v>6</v>
       </c>
-      <c r="G246" s="11" t="s">
+      <c r="G246" s="8" t="s">
         <v>1337</v>
       </c>
       <c r="H246" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="I246" s="3">
-        <v>0</v>
-      </c>
-      <c r="J246" s="14" t="s">
+      <c r="I246" s="2">
+        <v>0</v>
+      </c>
+      <c r="J246" s="13" t="s">
         <v>1339</v>
       </c>
-      <c r="K246" s="15" t="s">
+      <c r="K246" s="14" t="s">
         <v>1340</v>
       </c>
-      <c r="L246" s="13" t="s">
+      <c r="L246" s="12" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -12897,16 +13253,16 @@
       <c r="C247" s="1">
         <v>1241</v>
       </c>
-      <c r="D247" s="2" t="s">
+      <c r="D247" s="5" t="s">
         <v>1342</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E247" s="5">
         <v>6</v>
       </c>
-      <c r="F247" s="2">
+      <c r="F247" s="5">
         <v>6</v>
       </c>
-      <c r="G247" s="11" t="s">
+      <c r="G247" s="8" t="s">
         <v>1343</v>
       </c>
       <c r="H247" s="1" t="s">
@@ -12915,13 +13271,13 @@
       <c r="I247" s="1">
         <v>0</v>
       </c>
-      <c r="J247" s="14" t="s">
+      <c r="J247" s="13" t="s">
         <v>1339</v>
       </c>
-      <c r="K247" s="17" t="s">
+      <c r="K247" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="L247" s="13" t="s">
+      <c r="L247" s="12" t="s">
         <v>1345</v>
       </c>
     </row>
@@ -12929,16 +13285,16 @@
       <c r="C248" s="1">
         <v>1242</v>
       </c>
-      <c r="D248" s="2" t="s">
+      <c r="D248" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="E248" s="2">
+      <c r="E248" s="5">
         <v>6</v>
       </c>
-      <c r="F248" s="2">
+      <c r="F248" s="5">
         <v>6</v>
       </c>
-      <c r="G248" s="11" t="s">
+      <c r="G248" s="8" t="s">
         <v>1347</v>
       </c>
       <c r="H248" s="1" t="s">
@@ -12947,13 +13303,13 @@
       <c r="I248" s="1">
         <v>0</v>
       </c>
-      <c r="J248" s="14" t="s">
+      <c r="J248" s="13" t="s">
         <v>1339</v>
       </c>
-      <c r="K248" s="17" t="s">
+      <c r="K248" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="L248" s="13" t="s">
+      <c r="L248" s="12" t="s">
         <v>1349</v>
       </c>
     </row>
@@ -12961,16 +13317,16 @@
       <c r="C249" s="1">
         <v>1243</v>
       </c>
-      <c r="D249" s="2" t="s">
+      <c r="D249" s="5" t="s">
         <v>1350</v>
       </c>
-      <c r="E249" s="2">
+      <c r="E249" s="5">
         <v>6</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="5">
         <v>6</v>
       </c>
-      <c r="G249" s="11" t="s">
+      <c r="G249" s="8" t="s">
         <v>1351</v>
       </c>
       <c r="H249" s="1" t="s">
@@ -12979,13 +13335,13 @@
       <c r="I249" s="1">
         <v>0</v>
       </c>
-      <c r="J249" s="14" t="s">
+      <c r="J249" s="13" t="s">
         <v>1339</v>
       </c>
-      <c r="K249" s="17" t="s">
+      <c r="K249" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="L249" s="13" t="s">
+      <c r="L249" s="12" t="s">
         <v>1353</v>
       </c>
     </row>
@@ -12993,16 +13349,16 @@
       <c r="C250" s="1">
         <v>1244</v>
       </c>
-      <c r="D250" s="2" t="s">
+      <c r="D250" s="5" t="s">
         <v>1354</v>
       </c>
-      <c r="E250" s="2">
+      <c r="E250" s="5">
         <v>6</v>
       </c>
-      <c r="F250" s="2">
+      <c r="F250" s="5">
         <v>6</v>
       </c>
-      <c r="G250" s="11" t="s">
+      <c r="G250" s="8" t="s">
         <v>1355</v>
       </c>
       <c r="H250" s="1" t="s">
@@ -13011,13 +13367,13 @@
       <c r="I250" s="1">
         <v>0</v>
       </c>
-      <c r="J250" s="14" t="s">
+      <c r="J250" s="13" t="s">
         <v>1339</v>
       </c>
-      <c r="K250" s="17" t="s">
+      <c r="K250" s="13" t="s">
         <v>1340</v>
       </c>
-      <c r="L250" s="13" t="s">
+      <c r="L250" s="12" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -13038,4 +13394,1439 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:M40"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="3" width="9.25454545454545" customWidth="1"/>
+    <col min="4" max="7" width="11.6272727272727" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="11.6272727272727" customWidth="1"/>
+    <col min="10" max="10" width="61.0909090909091" customWidth="1"/>
+    <col min="11" max="11" width="62.8181818181818" customWidth="1"/>
+    <col min="12" max="12" width="12.5454545454545" customWidth="1"/>
+    <col min="13" max="13" width="70.3636363636364" customWidth="1"/>
+    <col min="14" max="16384" width="9.25454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="1">
+        <v>1245</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E6" s="2">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="1">
+        <v>1246</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E7" s="5">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>1366</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="1">
+        <v>1247</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5">
+        <v>6</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>1370</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="1">
+        <v>1248</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E9" s="5">
+        <v>6</v>
+      </c>
+      <c r="F9" s="5">
+        <v>6</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>1374</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="1">
+        <v>1249</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E10" s="5">
+        <v>6</v>
+      </c>
+      <c r="F10" s="5">
+        <v>6</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1250</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E11" s="5">
+        <v>6</v>
+      </c>
+      <c r="F11" s="5">
+        <v>6</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>1232</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A12" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1251</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E12" s="5">
+        <v>6</v>
+      </c>
+      <c r="F12" s="5">
+        <v>6</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A13" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1252</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E13" s="5">
+        <v>6</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A14" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1253</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E14" s="5">
+        <v>6</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A15" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1254</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E15" s="5">
+        <v>6</v>
+      </c>
+      <c r="F15" s="5">
+        <v>6</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>1383</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="18" customHeight="1" spans="1:13">
+      <c r="A16" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1255</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E16" s="5">
+        <v>6</v>
+      </c>
+      <c r="F16" s="5">
+        <v>6</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A17" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1256</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E17" s="5">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L17" s="12" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A18" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1257</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E18" s="5">
+        <v>6</v>
+      </c>
+      <c r="F18" s="5">
+        <v>6</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>1262</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A19" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1258</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E19" s="5">
+        <v>6</v>
+      </c>
+      <c r="F19" s="5">
+        <v>6</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A20" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1259</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E20" s="5">
+        <v>6</v>
+      </c>
+      <c r="F20" s="5">
+        <v>6</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="I20" s="1">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L20" s="12" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A21" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1260</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E21" s="5">
+        <v>6</v>
+      </c>
+      <c r="F21" s="5">
+        <v>6</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A22" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1261</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E22" s="5">
+        <v>6</v>
+      </c>
+      <c r="F22" s="5">
+        <v>6</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="I22" s="1">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A23" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1262</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E23" s="5">
+        <v>6</v>
+      </c>
+      <c r="F23" s="5">
+        <v>6</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A24" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1263</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E24" s="5">
+        <v>6</v>
+      </c>
+      <c r="F24" s="5">
+        <v>6</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I24" s="1">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A25" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1264</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E25" s="5">
+        <v>6</v>
+      </c>
+      <c r="F25" s="5">
+        <v>6</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A26" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1265</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E26" s="5">
+        <v>6</v>
+      </c>
+      <c r="F26" s="5">
+        <v>6</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A27" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1266</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E27" s="5">
+        <v>6</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L27" s="12" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A28" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1267</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E28" s="5">
+        <v>6</v>
+      </c>
+      <c r="F28" s="5">
+        <v>6</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L28" s="12" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A29" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1268</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E29" s="5">
+        <v>6</v>
+      </c>
+      <c r="F29" s="5">
+        <v>6</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>1308</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="I29" s="1">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L29" s="12" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A30" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1269</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E30" s="5">
+        <v>6</v>
+      </c>
+      <c r="F30" s="5">
+        <v>6</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A31" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1270</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E31" s="5">
+        <v>6</v>
+      </c>
+      <c r="F31" s="5">
+        <v>6</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A32" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1271</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E32" s="5">
+        <v>6</v>
+      </c>
+      <c r="F32" s="5">
+        <v>6</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>1321</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="I32" s="1">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A33" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1272</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E33" s="5">
+        <v>6</v>
+      </c>
+      <c r="F33" s="5">
+        <v>6</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>1325</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I33" s="1">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L33" s="12" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A34" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1273</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E34" s="5">
+        <v>6</v>
+      </c>
+      <c r="F34" s="5">
+        <v>6</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I34" s="1">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L34" s="12" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A35" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1274</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E35" s="5">
+        <v>6</v>
+      </c>
+      <c r="F35" s="5">
+        <v>6</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>1447</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A36" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1275</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E36" s="5">
+        <v>6</v>
+      </c>
+      <c r="F36" s="5">
+        <v>6</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A37" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1276</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E37" s="5">
+        <v>6</v>
+      </c>
+      <c r="F37" s="5">
+        <v>6</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="I37" s="1">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A38" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1277</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E38" s="5">
+        <v>6</v>
+      </c>
+      <c r="F38" s="5">
+        <v>6</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I38" s="1">
+        <v>0</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A39" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1278</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E39" s="5">
+        <v>6</v>
+      </c>
+      <c r="F39" s="5">
+        <v>6</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="18" customHeight="1" spans="1:12">
+      <c r="A40" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1279</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E40" s="5">
+        <v>6</v>
+      </c>
+      <c r="F40" s="5">
+        <v>6</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="I40" s="1">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>1463</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4674,12 +4674,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
